--- a/Sprint-7/DA103_S7_Datafile_Practice.xlsx
+++ b/Sprint-7/DA103_S7_Datafile_Practice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A_GPS_Activity\2024_2025\December\DA103\Sprint 7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LEARN_NIIT\Gitcode\JijuDataAnalyticsCodes\Sprint-7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DDFFD6-FF3A-4EAC-8713-A02CD9D4CE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7255EAFD-E44E-4481-A8F3-11FD583098C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mall Data" sheetId="1" r:id="rId1"/>
@@ -25,18 +25,42 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Task 3'!$A$2:$B$367</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">'Task 1'!$A$3</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'Task 1'!$A$4:$A$367</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Task 3'!$A$3</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Task 3'!$A$4:$A$354</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'Task 3'!$B$3</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'Task 3'!$B$4:$B$354</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'Task 1'!$D$3</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'Task 1'!$D$4:$D$263</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'Task 1'!$C$3</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'Task 1'!$C$4:$C$263</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'Task 1'!$D$3</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'Task 1'!$D$4:$D$263</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'Task 1'!$C$3</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'Task 1'!$C$4:$C$263</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'Task 1'!$D$3</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'Task 1'!$D$4:$D$263</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">'Task 1'!$B$3</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'Task 1'!$C$3</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">'Task 1'!$C$4:$C$263</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">'Task 1'!$D$3</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">'Task 1'!$D$4:$D$263</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">'Task 1'!$A$3</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">'Task 1'!$A$4:$A$367</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">'Task 1'!$B$3</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">'Task 1'!$B$4:$B$367</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">'Task 2'!$A$3</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">'Task 2'!$A$4:$A$191</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">'Task 1'!$B$4:$B$367</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Task 2'!$A$3</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Task 2'!$A$4:$A$191</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Task 2'!$B$3</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'Task 2'!$B$4:$B$191</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'Task 2'!$C$3</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'Task 2'!$C$4:$C$191</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">'Task 2'!$B$3</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">'Task 2'!$B$4:$B$191</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">'Task 2'!$C$3</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">'Task 2'!$C$4:$C$191</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'Task 3'!$A$3</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">'Task 3'!$A$4:$A$354</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">'Task 3'!$B$3</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">'Task 3'!$B$4:$B$354</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Task 1'!$C$3</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'Task 1'!$C$4:$C$263</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'Task 1'!$D$3</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'Task 1'!$D$4:$D$263</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'Task 1'!$C$3</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'Task 1'!$C$4:$C$263</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -231,10 +255,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -281,7 +305,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +327,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,13 +444,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -449,15 +479,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -471,7 +501,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -555,13 +585,55 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -589,12 +661,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.25</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.27</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -604,7 +676,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{29D891D9-FFD8-4D10-9E34-D1AFACCB07B4}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:f>_xlchart.v1.24</cx:f>
               <cx:v>Weekday</cx:v>
             </cx:txData>
           </cx:tx>
@@ -613,6 +685,9 @@
               <a:srgbClr val="FFC1EC"/>
             </a:solidFill>
           </cx:spPr>
+          <cx:dataLabels pos="t">
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
           <cx:dataId val="0"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -622,7 +697,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{BC2029C3-D5EB-41B3-A4E3-78F5AAA04813}" formatIdx="2">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:f>_xlchart.v1.26</cx:f>
               <cx:v>Weekend</cx:v>
             </cx:txData>
           </cx:tx>
@@ -631,6 +706,9 @@
               <a:srgbClr val="BDFFBD"/>
             </a:solidFill>
           </cx:spPr>
+          <cx:dataLabels pos="t">
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
           <cx:dataId val="1"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -760,17 +838,108 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.21</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.23</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{0B20D887-2914-4D88-B2E9-06EB941E5FED}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.20</cx:f>
+              <cx:v>Weekday</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels pos="t">
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{EE2A8998-E3F9-416D-AD19-1450D4A0FF02}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.22</cx:f>
+              <cx:v>Weekend</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels pos="t">
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Total Footfall</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent6"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                </a:rPr>
+                <a:t>Total Footfall</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="b" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.29</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.31</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.9</cx:f>
+        <cx:f>_xlchart.v1.33</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -780,7 +949,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{AB330EDE-9684-4951-82BD-988C40B51040}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.4</cx:f>
+              <cx:f>_xlchart.v1.28</cx:f>
               <cx:v>Morning</cx:v>
             </cx:txData>
           </cx:tx>
@@ -801,7 +970,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{FF8F9ACD-B485-4848-9607-58C62FDA6061}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.6</cx:f>
+              <cx:f>_xlchart.v1.30</cx:f>
               <cx:v>Afternoon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -819,7 +988,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{6471D082-8BB6-40F5-A0B5-60400189187F}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.8</cx:f>
+              <cx:f>_xlchart.v1.32</cx:f>
               <cx:v>Evening</cx:v>
             </cx:txData>
           </cx:tx>
@@ -952,17 +1121,17 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.11</cx:f>
+        <cx:f>_xlchart.v1.35</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.13</cx:f>
+        <cx:f>_xlchart.v1.37</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -972,7 +1141,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{D407F8AA-6457-4F6A-A783-7EB973693B06}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.10</cx:f>
+              <cx:f>_xlchart.v1.34</cx:f>
               <cx:v>Not Holiday</cx:v>
             </cx:txData>
           </cx:tx>
@@ -990,7 +1159,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{FE5B903E-6EFE-4A6F-A638-740BC563ABF2}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.12</cx:f>
+              <cx:f>_xlchart.v1.36</cx:f>
               <cx:v>Holiday</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1204,6 +1373,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2788,6 +2997,521 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
@@ -3078,7 +3802,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
+                <a:rPr lang="en-ZA" sz="1100"/>
                 <a:t>This chart isn't available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
@@ -3238,6 +3962,84 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Chart 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66A12F8D-5311-7C64-926F-2318CA3D80E9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11849100" y="1143000"/>
+              <a:ext cx="4053840" cy="3230880"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-ZA" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3484,7 +4286,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
+                <a:rPr lang="en-ZA" sz="1100"/>
                 <a:t>This chart isn't available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
@@ -3839,7 +4641,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-IN" sz="1100"/>
+                <a:rPr lang="en-ZA" sz="1100"/>
                 <a:t>This chart isn't available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
@@ -28830,7 +29632,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="10" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="10" width="11.88671875" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="14.109375" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
@@ -28920,8 +29724,14 @@
       <c r="F3" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="18"/>
+      <c r="G3" s="23">
+        <f>QUARTILE(A4:A263,1)</f>
+        <v>11314.75</v>
+      </c>
+      <c r="H3" s="18">
+        <f>QUARTILE(B4:B108,1)</f>
+        <v>23877</v>
+      </c>
       <c r="L3" s="7" t="s">
         <v>29</v>
       </c>
@@ -28936,8 +29746,14 @@
       <c r="P3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
+      <c r="Q3" s="16">
+        <f>AVERAGE(C4:C263)</f>
+        <v>14641.865384615385</v>
+      </c>
+      <c r="R3" s="16">
+        <f>AVERAGE(D4:D108)</f>
+        <v>28018.323809523808</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="33">
@@ -28946,14 +29762,24 @@
       <c r="B4" s="33">
         <v>25459</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="33">
+        <v>14593</v>
+      </c>
+      <c r="D4" s="33">
+        <v>25459</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="18"/>
+      <c r="G4" s="23">
+        <f>QUARTILE(A4:A263,3)</f>
+        <v>17331</v>
+      </c>
+      <c r="H4" s="18">
+        <f>QUARTILE(B4:B108,3)</f>
+        <v>31483</v>
+      </c>
       <c r="I4" s="20"/>
       <c r="J4" s="20"/>
       <c r="K4" s="2"/>
@@ -28971,8 +29797,14 @@
       <c r="P4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+      <c r="Q4" s="16">
+        <f>MEDIAN(C4:C263)</f>
+        <v>14039.5</v>
+      </c>
+      <c r="R4" s="16">
+        <f>MEDIAN(D4:D108)</f>
+        <v>28345</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
@@ -28981,14 +29813,24 @@
       <c r="B5" s="33">
         <v>40986</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="C5" s="33">
+        <v>17912</v>
+      </c>
+      <c r="D5" s="33">
+        <v>40986</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="G5" s="19">
+        <f>G4-G3</f>
+        <v>6016.25</v>
+      </c>
+      <c r="H5" s="19">
+        <f>H4-H3</f>
+        <v>7606</v>
+      </c>
       <c r="I5" s="20"/>
       <c r="J5" s="20"/>
       <c r="K5" s="2"/>
@@ -29006,8 +29848,14 @@
       <c r="P5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
+      <c r="Q5" s="16">
+        <f>MODE(C4:C263)</f>
+        <v>26355</v>
+      </c>
+      <c r="R5" s="16">
+        <f>MODE(D4:D108)</f>
+        <v>33673</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="33">
@@ -29016,14 +29864,24 @@
       <c r="B6" s="33">
         <v>24064</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="C6" s="33">
+        <v>15301</v>
+      </c>
+      <c r="D6" s="33">
+        <v>24064</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="G6" s="19">
+        <f>G3-1.5*G5</f>
+        <v>2290.375</v>
+      </c>
+      <c r="H6" s="19">
+        <f>H3-1.5*H5</f>
+        <v>12468</v>
+      </c>
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
       <c r="K6" s="2"/>
@@ -29035,14 +29893,24 @@
       <c r="B7" s="33">
         <v>22911</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="C7" s="33">
+        <v>18676</v>
+      </c>
+      <c r="D7" s="33">
+        <v>22911</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="G7" s="19">
+        <f>G4+1.5*G5</f>
+        <v>26355.375</v>
+      </c>
+      <c r="H7" s="19">
+        <f>H4+1.5*H5</f>
+        <v>42892</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -29060,8 +29928,12 @@
       <c r="B8" s="33">
         <v>29735</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="C8" s="33">
+        <v>13637</v>
+      </c>
+      <c r="D8" s="33">
+        <v>29735</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -29083,8 +29955,12 @@
       <c r="B9" s="33">
         <v>31707</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="C9" s="33">
+        <v>8532</v>
+      </c>
+      <c r="D9" s="33">
+        <v>31707</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -29106,8 +29982,12 @@
       <c r="B10" s="33">
         <v>29219</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="C10" s="33">
+        <v>12188</v>
+      </c>
+      <c r="D10" s="33">
+        <v>29219</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -29129,8 +30009,12 @@
       <c r="B11" s="33">
         <v>32041</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="C11" s="33">
+        <v>19487</v>
+      </c>
+      <c r="D11" s="33">
+        <v>32041</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -29152,8 +30036,12 @@
       <c r="B12" s="33">
         <v>34172</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="C12" s="33">
+        <v>8031</v>
+      </c>
+      <c r="D12" s="33">
+        <v>34172</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -29175,8 +30063,12 @@
       <c r="B13" s="33">
         <v>21683</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="C13" s="33">
+        <v>13022</v>
+      </c>
+      <c r="D13" s="33">
+        <v>21683</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -29198,8 +30090,12 @@
       <c r="B14" s="33">
         <v>32985</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="C14" s="33">
+        <v>9712</v>
+      </c>
+      <c r="D14" s="33">
+        <v>32985</v>
+      </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -29221,8 +30117,12 @@
       <c r="B15" s="33">
         <v>22113</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="C15" s="33">
+        <v>16160</v>
+      </c>
+      <c r="D15" s="33">
+        <v>22113</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -29244,8 +30144,12 @@
       <c r="B16" s="33">
         <v>29637</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="C16" s="33">
+        <v>14179</v>
+      </c>
+      <c r="D16" s="33">
+        <v>29637</v>
+      </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -29267,8 +30171,12 @@
       <c r="B17" s="33">
         <v>29223</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="C17" s="33">
+        <v>17045</v>
+      </c>
+      <c r="D17" s="33">
+        <v>29223</v>
+      </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -29290,8 +30198,12 @@
       <c r="B18" s="33">
         <v>27823</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="C18" s="33">
+        <v>17275</v>
+      </c>
+      <c r="D18" s="33">
+        <v>27823</v>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -29310,8 +30222,12 @@
       <c r="B19" s="33">
         <v>31669</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="C19" s="33">
+        <v>18194</v>
+      </c>
+      <c r="D19" s="33">
+        <v>31669</v>
+      </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -29327,8 +30243,12 @@
       <c r="B20" s="33">
         <v>23675</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="C20" s="33">
+        <v>13707</v>
+      </c>
+      <c r="D20" s="33">
+        <v>23675</v>
+      </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -29344,8 +30264,12 @@
       <c r="B21" s="33">
         <v>29271</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+      <c r="C21" s="33">
+        <v>19298</v>
+      </c>
+      <c r="D21" s="33">
+        <v>29271</v>
+      </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -29361,8 +30285,12 @@
       <c r="B22" s="33">
         <v>33863</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="C22" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D22" s="33">
+        <v>33863</v>
+      </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -29378,8 +30306,12 @@
       <c r="B23" s="33">
         <v>25103</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="C23" s="33">
+        <v>14080</v>
+      </c>
+      <c r="D23" s="33">
+        <v>25103</v>
+      </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -29395,8 +30327,12 @@
       <c r="B24" s="33">
         <v>33673</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="C24" s="33">
+        <v>18768</v>
+      </c>
+      <c r="D24" s="33">
+        <v>33673</v>
+      </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -29412,8 +30348,12 @@
       <c r="B25" s="33">
         <v>33673</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="C25" s="33">
+        <v>10849</v>
+      </c>
+      <c r="D25" s="33">
+        <v>33673</v>
+      </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -29429,8 +30369,12 @@
       <c r="B26" s="33">
         <v>27323</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="C26" s="33">
+        <v>12960</v>
+      </c>
+      <c r="D26" s="33">
+        <v>27323</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -29446,8 +30390,12 @@
       <c r="B27" s="33">
         <v>28345</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="C27" s="33">
+        <v>14543</v>
+      </c>
+      <c r="D27" s="33">
+        <v>28345</v>
+      </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -29463,8 +30411,12 @@
       <c r="B28" s="33">
         <v>33673</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="C28" s="33">
+        <v>11870</v>
+      </c>
+      <c r="D28" s="33">
+        <v>33673</v>
+      </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -29480,8 +30432,12 @@
       <c r="B29" s="33">
         <v>31138</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="C29" s="33">
+        <v>13453</v>
+      </c>
+      <c r="D29" s="33">
+        <v>31138</v>
+      </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -29497,8 +30453,12 @@
       <c r="B30" s="33">
         <v>31483</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="C30" s="33">
+        <v>11221</v>
+      </c>
+      <c r="D30" s="33">
+        <v>31483</v>
+      </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -29514,8 +30474,12 @@
       <c r="B31" s="33">
         <v>33386</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="C31" s="33">
+        <v>10828</v>
+      </c>
+      <c r="D31" s="33">
+        <v>33386</v>
+      </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -29531,8 +30495,12 @@
       <c r="B32" s="33">
         <v>29749</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="C32" s="33">
+        <v>18708</v>
+      </c>
+      <c r="D32" s="33">
+        <v>29749</v>
+      </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -29548,8 +30516,12 @@
       <c r="B33" s="33">
         <v>23210</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="C33" s="33">
+        <v>10713</v>
+      </c>
+      <c r="D33" s="33">
+        <v>23210</v>
+      </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -29565,8 +30537,12 @@
       <c r="B34" s="33">
         <v>33062</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="C34" s="33">
+        <v>13898</v>
+      </c>
+      <c r="D34" s="33">
+        <v>33062</v>
+      </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -29582,8 +30558,12 @@
       <c r="B35" s="33">
         <v>30444</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="C35" s="33">
+        <v>16368</v>
+      </c>
+      <c r="D35" s="33">
+        <v>30444</v>
+      </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -29599,8 +30579,12 @@
       <c r="B36" s="33">
         <v>23623</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="C36" s="33">
+        <v>11776</v>
+      </c>
+      <c r="D36" s="33">
+        <v>23623</v>
+      </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -29616,8 +30600,12 @@
       <c r="B37" s="33">
         <v>23752</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+      <c r="C37" s="33">
+        <v>12682</v>
+      </c>
+      <c r="D37" s="33">
+        <v>23752</v>
+      </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -29633,8 +30621,12 @@
       <c r="B38" s="33">
         <v>34473</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="C38" s="33">
+        <v>9830</v>
+      </c>
+      <c r="D38" s="33">
+        <v>34473</v>
+      </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -29650,8 +30642,12 @@
       <c r="B39" s="33">
         <v>26615</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="C39" s="33">
+        <v>18922</v>
+      </c>
+      <c r="D39" s="33">
+        <v>26615</v>
+      </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -29667,8 +30663,12 @@
       <c r="B40" s="33">
         <v>30803</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
+      <c r="C40" s="33">
+        <v>17625</v>
+      </c>
+      <c r="D40" s="33">
+        <v>30803</v>
+      </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -29684,8 +30684,12 @@
       <c r="B41" s="33">
         <v>29833</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="C41" s="33">
+        <v>14396</v>
+      </c>
+      <c r="D41" s="33">
+        <v>29833</v>
+      </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -29701,8 +30705,12 @@
       <c r="B42" s="33">
         <v>30934</v>
       </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="C42" s="33">
+        <v>11783</v>
+      </c>
+      <c r="D42" s="33">
+        <v>30934</v>
+      </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -29718,8 +30726,12 @@
       <c r="B43" s="33">
         <v>34021</v>
       </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="C43" s="33">
+        <v>12457</v>
+      </c>
+      <c r="D43" s="33">
+        <v>34021</v>
+      </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -29735,8 +30747,12 @@
       <c r="B44" s="33">
         <v>22800</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="C44" s="33">
+        <v>19439</v>
+      </c>
+      <c r="D44" s="33">
+        <v>22800</v>
+      </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -29752,8 +30768,12 @@
       <c r="B45" s="33">
         <v>31349</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
+      <c r="C45" s="33">
+        <v>11720</v>
+      </c>
+      <c r="D45" s="33">
+        <v>31349</v>
+      </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -29769,8 +30789,12 @@
       <c r="B46" s="33">
         <v>23141</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="C46" s="33">
+        <v>9919</v>
+      </c>
+      <c r="D46" s="33">
+        <v>23141</v>
+      </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -29786,8 +30810,12 @@
       <c r="B47" s="33">
         <v>31017</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="C47" s="33">
+        <v>10189</v>
+      </c>
+      <c r="D47" s="33">
+        <v>31017</v>
+      </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -29803,8 +30831,12 @@
       <c r="B48" s="33">
         <v>30446</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="C48" s="33">
+        <v>17272</v>
+      </c>
+      <c r="D48" s="33">
+        <v>30446</v>
+      </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -29820,8 +30852,12 @@
       <c r="B49" s="33">
         <v>29680</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="C49" s="33">
+        <v>16084</v>
+      </c>
+      <c r="D49" s="33">
+        <v>29680</v>
+      </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -29837,8 +30873,12 @@
       <c r="B50" s="33">
         <v>34299</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="C50" s="33">
+        <v>19384</v>
+      </c>
+      <c r="D50" s="33">
+        <v>34299</v>
+      </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -29854,8 +30894,12 @@
       <c r="B51" s="33">
         <v>31147</v>
       </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+      <c r="C51" s="33">
+        <v>10998</v>
+      </c>
+      <c r="D51" s="33">
+        <v>31147</v>
+      </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -29871,8 +30915,12 @@
       <c r="B52" s="33">
         <v>33961</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="C52" s="33">
+        <v>11057</v>
+      </c>
+      <c r="D52" s="33">
+        <v>33961</v>
+      </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -29888,8 +30936,12 @@
       <c r="B53" s="33">
         <v>20770</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="C53" s="33">
+        <v>9837</v>
+      </c>
+      <c r="D53" s="33">
+        <v>20770</v>
+      </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -29905,8 +30957,12 @@
       <c r="B54" s="33">
         <v>29350</v>
       </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="C54" s="33">
+        <v>17777</v>
+      </c>
+      <c r="D54" s="33">
+        <v>29350</v>
+      </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -29922,8 +30978,12 @@
       <c r="B55" s="33">
         <v>26100</v>
       </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="C55" s="33">
+        <v>14077</v>
+      </c>
+      <c r="D55" s="33">
+        <v>26100</v>
+      </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -29939,8 +30999,12 @@
       <c r="B56" s="33">
         <v>23487</v>
       </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
+      <c r="C56" s="33">
+        <v>17340</v>
+      </c>
+      <c r="D56" s="33">
+        <v>23487</v>
+      </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -29956,8 +31020,12 @@
       <c r="B57" s="33">
         <v>20977</v>
       </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
+      <c r="C57" s="33">
+        <v>19230</v>
+      </c>
+      <c r="D57" s="33">
+        <v>20977</v>
+      </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -29973,8 +31041,12 @@
       <c r="B58" s="33">
         <v>33555</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="C58" s="33">
+        <v>12498</v>
+      </c>
+      <c r="D58" s="33">
+        <v>33555</v>
+      </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -29990,8 +31062,12 @@
       <c r="B59" s="33">
         <v>21427</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
+      <c r="C59" s="33">
+        <v>12032</v>
+      </c>
+      <c r="D59" s="33">
+        <v>21427</v>
+      </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -30007,8 +31083,12 @@
       <c r="B60" s="33">
         <v>34543</v>
       </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
+      <c r="C60" s="33">
+        <v>16592</v>
+      </c>
+      <c r="D60" s="33">
+        <v>34543</v>
+      </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -30024,8 +31104,12 @@
       <c r="B61" s="33">
         <v>30459</v>
       </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
+      <c r="C61" s="33">
+        <v>9785</v>
+      </c>
+      <c r="D61" s="33">
+        <v>30459</v>
+      </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -30041,8 +31125,12 @@
       <c r="B62" s="33">
         <v>28288</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="C62" s="33">
+        <v>13500</v>
+      </c>
+      <c r="D62" s="33">
+        <v>28288</v>
+      </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -30058,8 +31146,12 @@
       <c r="B63" s="33">
         <v>26849</v>
       </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
+      <c r="C63" s="33">
+        <v>12039</v>
+      </c>
+      <c r="D63" s="33">
+        <v>26849</v>
+      </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -30075,8 +31167,12 @@
       <c r="B64" s="33">
         <v>33074</v>
       </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+      <c r="C64" s="33">
+        <v>9015</v>
+      </c>
+      <c r="D64" s="33">
+        <v>33074</v>
+      </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -30092,8 +31188,12 @@
       <c r="B65" s="33">
         <v>28327</v>
       </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
+      <c r="C65" s="33">
+        <v>10921</v>
+      </c>
+      <c r="D65" s="33">
+        <v>28327</v>
+      </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -30109,8 +31209,12 @@
       <c r="B66" s="33">
         <v>27032</v>
       </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
+      <c r="C66" s="33">
+        <v>14844</v>
+      </c>
+      <c r="D66" s="33">
+        <v>27032</v>
+      </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -30126,8 +31230,12 @@
       <c r="B67" s="33">
         <v>22394</v>
       </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
+      <c r="C67" s="33">
+        <v>19352</v>
+      </c>
+      <c r="D67" s="33">
+        <v>22394</v>
+      </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -30143,8 +31251,12 @@
       <c r="B68" s="33">
         <v>27899</v>
       </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
+      <c r="C68" s="33">
+        <v>8040</v>
+      </c>
+      <c r="D68" s="33">
+        <v>27899</v>
+      </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -30160,8 +31272,12 @@
       <c r="B69" s="33">
         <v>20459</v>
       </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+      <c r="C69" s="33">
+        <v>15147</v>
+      </c>
+      <c r="D69" s="33">
+        <v>20459</v>
+      </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -30177,8 +31293,12 @@
       <c r="B70" s="33">
         <v>27272</v>
       </c>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
+      <c r="C70" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D70" s="33">
+        <v>27272</v>
+      </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -30194,8 +31314,12 @@
       <c r="B71" s="33">
         <v>24503</v>
       </c>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
+      <c r="C71" s="33">
+        <v>12665</v>
+      </c>
+      <c r="D71" s="33">
+        <v>24503</v>
+      </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -30211,8 +31335,12 @@
       <c r="B72" s="33">
         <v>32531</v>
       </c>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
+      <c r="C72" s="33">
+        <v>15050</v>
+      </c>
+      <c r="D72" s="33">
+        <v>32531</v>
+      </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -30228,8 +31356,12 @@
       <c r="B73" s="33">
         <v>25455</v>
       </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+      <c r="C73" s="33">
+        <v>10239</v>
+      </c>
+      <c r="D73" s="33">
+        <v>25455</v>
+      </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -30245,8 +31377,12 @@
       <c r="B74" s="33">
         <v>24998</v>
       </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
+      <c r="C74" s="33">
+        <v>17150</v>
+      </c>
+      <c r="D74" s="33">
+        <v>24998</v>
+      </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -30262,8 +31398,12 @@
       <c r="B75" s="33">
         <v>28972</v>
       </c>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+      <c r="C75" s="33">
+        <v>19805</v>
+      </c>
+      <c r="D75" s="33">
+        <v>28972</v>
+      </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -30279,8 +31419,12 @@
       <c r="B76" s="33">
         <v>22079</v>
       </c>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
+      <c r="C76" s="33">
+        <v>17328</v>
+      </c>
+      <c r="D76" s="33">
+        <v>22079</v>
+      </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -30296,8 +31440,12 @@
       <c r="B77" s="33">
         <v>23427</v>
       </c>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
+      <c r="C77" s="33">
+        <v>12529</v>
+      </c>
+      <c r="D77" s="33">
+        <v>23427</v>
+      </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -30313,8 +31461,12 @@
       <c r="B78" s="33">
         <v>22409</v>
       </c>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
+      <c r="C78" s="33">
+        <v>9200</v>
+      </c>
+      <c r="D78" s="33">
+        <v>22409</v>
+      </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -30330,8 +31482,12 @@
       <c r="B79" s="33">
         <v>20279</v>
       </c>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
+      <c r="C79" s="33">
+        <v>18667</v>
+      </c>
+      <c r="D79" s="33">
+        <v>20279</v>
+      </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -30347,8 +31503,12 @@
       <c r="B80" s="33">
         <v>34142</v>
       </c>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
+      <c r="C80" s="33">
+        <v>15532</v>
+      </c>
+      <c r="D80" s="33">
+        <v>34142</v>
+      </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -30364,8 +31524,12 @@
       <c r="B81" s="33">
         <v>25309</v>
       </c>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
+      <c r="C81" s="33">
+        <v>10255</v>
+      </c>
+      <c r="D81" s="33">
+        <v>25309</v>
+      </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -30381,8 +31545,12 @@
       <c r="B82" s="33">
         <v>34719</v>
       </c>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
+      <c r="C82" s="33">
+        <v>11269</v>
+      </c>
+      <c r="D82" s="33">
+        <v>34719</v>
+      </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -30398,8 +31566,12 @@
       <c r="B83" s="33">
         <v>24339</v>
       </c>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
+      <c r="C83" s="33">
+        <v>14029</v>
+      </c>
+      <c r="D83" s="33">
+        <v>24339</v>
+      </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -30415,8 +31587,12 @@
       <c r="B84" s="33">
         <v>33028</v>
       </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
+      <c r="C84" s="33">
+        <v>10841</v>
+      </c>
+      <c r="D84" s="33">
+        <v>33028</v>
+      </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -30432,8 +31608,12 @@
       <c r="B85" s="33">
         <v>24445</v>
       </c>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
+      <c r="C85" s="33">
+        <v>9659</v>
+      </c>
+      <c r="D85" s="33">
+        <v>24445</v>
+      </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -30449,8 +31629,12 @@
       <c r="B86" s="33">
         <v>30830</v>
       </c>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
+      <c r="C86" s="33">
+        <v>17412</v>
+      </c>
+      <c r="D86" s="33">
+        <v>30830</v>
+      </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -30466,8 +31650,12 @@
       <c r="B87" s="33">
         <v>25222</v>
       </c>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
+      <c r="C87" s="33">
+        <v>9050</v>
+      </c>
+      <c r="D87" s="33">
+        <v>25222</v>
+      </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -30483,8 +31671,12 @@
       <c r="B88" s="33">
         <v>29450</v>
       </c>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
+      <c r="C88" s="33">
+        <v>10317</v>
+      </c>
+      <c r="D88" s="33">
+        <v>29450</v>
+      </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -30500,8 +31692,12 @@
       <c r="B89" s="33">
         <v>20031</v>
       </c>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
+      <c r="C89" s="33">
+        <v>10526</v>
+      </c>
+      <c r="D89" s="33">
+        <v>20031</v>
+      </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -30517,8 +31713,12 @@
       <c r="B90" s="33">
         <v>21218</v>
       </c>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
+      <c r="C90" s="33">
+        <v>13144</v>
+      </c>
+      <c r="D90" s="33">
+        <v>21218</v>
+      </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -30534,8 +31734,12 @@
       <c r="B91" s="33">
         <v>34961</v>
       </c>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
+      <c r="C91" s="33">
+        <v>19742</v>
+      </c>
+      <c r="D91" s="33">
+        <v>34961</v>
+      </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -30551,8 +31755,12 @@
       <c r="B92" s="33">
         <v>23877</v>
       </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
+      <c r="C92" s="33">
+        <v>14780</v>
+      </c>
+      <c r="D92" s="33">
+        <v>23877</v>
+      </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -30568,8 +31776,12 @@
       <c r="B93" s="33">
         <v>24137</v>
       </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
+      <c r="C93" s="33">
+        <v>9952</v>
+      </c>
+      <c r="D93" s="33">
+        <v>24137</v>
+      </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -30585,8 +31797,12 @@
       <c r="B94" s="33">
         <v>22399</v>
       </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
+      <c r="C94" s="33">
+        <v>9674</v>
+      </c>
+      <c r="D94" s="33">
+        <v>22399</v>
+      </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -30602,8 +31818,12 @@
       <c r="B95" s="33">
         <v>20226</v>
       </c>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
+      <c r="C95" s="33">
+        <v>16059</v>
+      </c>
+      <c r="D95" s="33">
+        <v>20226</v>
+      </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -30619,8 +31839,12 @@
       <c r="B96" s="33">
         <v>34353</v>
       </c>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
+      <c r="C96" s="33">
+        <v>13652</v>
+      </c>
+      <c r="D96" s="33">
+        <v>34353</v>
+      </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -30636,8 +31860,12 @@
       <c r="B97" s="33">
         <v>24626</v>
       </c>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
+      <c r="C97" s="33">
+        <v>9941</v>
+      </c>
+      <c r="D97" s="33">
+        <v>24626</v>
+      </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -30653,8 +31881,12 @@
       <c r="B98" s="33">
         <v>24422</v>
       </c>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
+      <c r="C98" s="33">
+        <v>13685</v>
+      </c>
+      <c r="D98" s="33">
+        <v>24422</v>
+      </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -30670,8 +31902,12 @@
       <c r="B99" s="33">
         <v>22596</v>
       </c>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
+      <c r="C99" s="33">
+        <v>17053</v>
+      </c>
+      <c r="D99" s="33">
+        <v>22596</v>
+      </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -30687,8 +31923,12 @@
       <c r="B100" s="33">
         <v>28043</v>
       </c>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
+      <c r="C100" s="33">
+        <v>16797</v>
+      </c>
+      <c r="D100" s="33">
+        <v>28043</v>
+      </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -30704,8 +31944,12 @@
       <c r="B101" s="33">
         <v>23206</v>
       </c>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
+      <c r="C101" s="33">
+        <v>11220</v>
+      </c>
+      <c r="D101" s="33">
+        <v>23206</v>
+      </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -30721,8 +31965,12 @@
       <c r="B102" s="33">
         <v>28299</v>
       </c>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
+      <c r="C102" s="33">
+        <v>14880</v>
+      </c>
+      <c r="D102" s="33">
+        <v>28299</v>
+      </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -30738,8 +31986,12 @@
       <c r="B103" s="33">
         <v>32890</v>
       </c>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
+      <c r="C103" s="33">
+        <v>12861</v>
+      </c>
+      <c r="D103" s="33">
+        <v>32890</v>
+      </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -30755,8 +32007,12 @@
       <c r="B104" s="33">
         <v>29651</v>
       </c>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
+      <c r="C104" s="33">
+        <v>11330</v>
+      </c>
+      <c r="D104" s="33">
+        <v>29651</v>
+      </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -30772,8 +32028,12 @@
       <c r="B105" s="33">
         <v>28602</v>
       </c>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
+      <c r="C105" s="33">
+        <v>12941</v>
+      </c>
+      <c r="D105" s="33">
+        <v>28602</v>
+      </c>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -30789,8 +32049,12 @@
       <c r="B106" s="33">
         <v>29412</v>
       </c>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
+      <c r="C106" s="33">
+        <v>9453</v>
+      </c>
+      <c r="D106" s="33">
+        <v>29412</v>
+      </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -30806,8 +32070,12 @@
       <c r="B107" s="33">
         <v>22042</v>
       </c>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
+      <c r="C107" s="33">
+        <v>16806</v>
+      </c>
+      <c r="D107" s="33">
+        <v>22042</v>
+      </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -30823,1248 +32091,1562 @@
       <c r="B108" s="33">
         <v>30142</v>
       </c>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
+      <c r="C108" s="33">
+        <v>16835</v>
+      </c>
+      <c r="D108" s="33">
+        <v>30142</v>
+      </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="33">
         <v>10087</v>
       </c>
       <c r="B109" s="33"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
+      <c r="C109" s="33">
+        <v>10087</v>
+      </c>
+      <c r="D109" s="33"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="33">
         <v>12757</v>
       </c>
       <c r="B110" s="33"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
+      <c r="C110" s="33">
+        <v>12757</v>
+      </c>
+      <c r="D110" s="33"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="33">
         <v>10766</v>
       </c>
       <c r="B111" s="33"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
+      <c r="C111" s="33">
+        <v>10766</v>
+      </c>
+      <c r="D111" s="33"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="33">
         <v>9434</v>
       </c>
       <c r="B112" s="33"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
+      <c r="C112" s="33">
+        <v>9434</v>
+      </c>
+      <c r="D112" s="33"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="33">
         <v>10397</v>
       </c>
       <c r="B113" s="33"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+      <c r="C113" s="33">
+        <v>10397</v>
+      </c>
+      <c r="D113" s="33"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="33">
         <v>17177</v>
       </c>
       <c r="B114" s="33"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
+      <c r="C114" s="33">
+        <v>17177</v>
+      </c>
+      <c r="D114" s="33"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="33">
         <v>12886</v>
       </c>
       <c r="B115" s="33"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
+      <c r="C115" s="33">
+        <v>12886</v>
+      </c>
+      <c r="D115" s="33"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="33">
         <v>12804</v>
       </c>
       <c r="B116" s="33"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
+      <c r="C116" s="33">
+        <v>12804</v>
+      </c>
+      <c r="D116" s="33"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="33">
         <v>10028</v>
       </c>
       <c r="B117" s="33"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
+      <c r="C117" s="33">
+        <v>10028</v>
+      </c>
+      <c r="D117" s="33"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="33">
         <v>13499</v>
       </c>
       <c r="B118" s="33"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
+      <c r="C118" s="33">
+        <v>13499</v>
+      </c>
+      <c r="D118" s="33"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="33">
         <v>15354</v>
       </c>
       <c r="B119" s="33"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
+      <c r="C119" s="33">
+        <v>15354</v>
+      </c>
+      <c r="D119" s="33"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="33">
         <v>14596</v>
       </c>
       <c r="B120" s="33"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
+      <c r="C120" s="33">
+        <v>14596</v>
+      </c>
+      <c r="D120" s="33"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="33">
         <v>18435</v>
       </c>
       <c r="B121" s="33"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
+      <c r="C121" s="33">
+        <v>18435</v>
+      </c>
+      <c r="D121" s="33"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="33">
         <v>11737</v>
       </c>
       <c r="B122" s="33"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
+      <c r="C122" s="33">
+        <v>11737</v>
+      </c>
+      <c r="D122" s="33"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="33">
         <v>12844</v>
       </c>
       <c r="B123" s="33"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
+      <c r="C123" s="33">
+        <v>12844</v>
+      </c>
+      <c r="D123" s="33"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="33">
         <v>11531</v>
       </c>
       <c r="B124" s="33"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
+      <c r="C124" s="33">
+        <v>11531</v>
+      </c>
+      <c r="D124" s="33"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="33">
         <v>11764</v>
       </c>
       <c r="B125" s="33"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
+      <c r="C125" s="33">
+        <v>11764</v>
+      </c>
+      <c r="D125" s="33"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="33">
         <v>15273</v>
       </c>
       <c r="B126" s="33"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
+      <c r="C126" s="33">
+        <v>15273</v>
+      </c>
+      <c r="D126" s="33"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="33">
         <v>18729</v>
       </c>
       <c r="B127" s="33"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
+      <c r="C127" s="33">
+        <v>18729</v>
+      </c>
+      <c r="D127" s="33"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="33">
         <v>9824</v>
       </c>
       <c r="B128" s="33"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
+      <c r="C128" s="33">
+        <v>9824</v>
+      </c>
+      <c r="D128" s="33"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="33">
         <v>12483</v>
       </c>
       <c r="B129" s="33"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
+      <c r="C129" s="33">
+        <v>12483</v>
+      </c>
+      <c r="D129" s="33"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="33">
         <v>14918</v>
       </c>
       <c r="B130" s="33"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
+      <c r="C130" s="33">
+        <v>14918</v>
+      </c>
+      <c r="D130" s="33"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="33">
         <v>17497</v>
       </c>
       <c r="B131" s="33"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
+      <c r="C131" s="33">
+        <v>17497</v>
+      </c>
+      <c r="D131" s="33"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="33">
         <v>14053</v>
       </c>
       <c r="B132" s="33"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
+      <c r="C132" s="33">
+        <v>14053</v>
+      </c>
+      <c r="D132" s="33"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="33">
         <v>8241</v>
       </c>
       <c r="B133" s="33"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
+      <c r="C133" s="33">
+        <v>8241</v>
+      </c>
+      <c r="D133" s="33"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="33">
         <v>10715</v>
       </c>
       <c r="B134" s="33"/>
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
+      <c r="C134" s="33">
+        <v>10715</v>
+      </c>
+      <c r="D134" s="33"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="33">
         <v>8352</v>
       </c>
       <c r="B135" s="33"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
+      <c r="C135" s="33">
+        <v>8352</v>
+      </c>
+      <c r="D135" s="33"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="33">
         <v>14982</v>
       </c>
       <c r="B136" s="33"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
+      <c r="C136" s="33">
+        <v>14982</v>
+      </c>
+      <c r="D136" s="33"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="33">
         <v>14732</v>
       </c>
       <c r="B137" s="33"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
+      <c r="C137" s="33">
+        <v>14732</v>
+      </c>
+      <c r="D137" s="33"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="33">
         <v>14050</v>
       </c>
       <c r="B138" s="33"/>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
+      <c r="C138" s="33">
+        <v>14050</v>
+      </c>
+      <c r="D138" s="33"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="33">
         <v>12755</v>
       </c>
       <c r="B139" s="33"/>
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
+      <c r="C139" s="33">
+        <v>12755</v>
+      </c>
+      <c r="D139" s="33"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="33">
         <v>12806</v>
       </c>
       <c r="B140" s="33"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
+      <c r="C140" s="33">
+        <v>12806</v>
+      </c>
+      <c r="D140" s="33"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="33">
         <v>14152</v>
       </c>
       <c r="B141" s="33"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
+      <c r="C141" s="33">
+        <v>14152</v>
+      </c>
+      <c r="D141" s="33"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="33">
         <v>12699</v>
       </c>
       <c r="B142" s="33"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
+      <c r="C142" s="33">
+        <v>12699</v>
+      </c>
+      <c r="D142" s="33"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="33">
         <v>18922</v>
       </c>
       <c r="B143" s="33"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
+      <c r="C143" s="33">
+        <v>18922</v>
+      </c>
+      <c r="D143" s="33"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="33">
         <v>18586</v>
       </c>
       <c r="B144" s="33"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
+      <c r="C144" s="33">
+        <v>18586</v>
+      </c>
+      <c r="D144" s="33"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="33">
         <v>14225</v>
       </c>
       <c r="B145" s="33"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
+      <c r="C145" s="33">
+        <v>14225</v>
+      </c>
+      <c r="D145" s="33"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="33">
         <v>8651</v>
       </c>
       <c r="B146" s="33"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
+      <c r="C146" s="33">
+        <v>8651</v>
+      </c>
+      <c r="D146" s="33"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="33">
         <v>19081</v>
       </c>
       <c r="B147" s="33"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
+      <c r="C147" s="33">
+        <v>19081</v>
+      </c>
+      <c r="D147" s="33"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="33">
         <v>24187</v>
       </c>
       <c r="B148" s="33"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
+      <c r="C148" s="33">
+        <v>24187</v>
+      </c>
+      <c r="D148" s="33"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="33">
         <v>19444</v>
       </c>
       <c r="B149" s="33"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
+      <c r="C149" s="33">
+        <v>19444</v>
+      </c>
+      <c r="D149" s="33"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="33">
         <v>18263</v>
       </c>
       <c r="B150" s="33"/>
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
+      <c r="C150" s="33">
+        <v>18263</v>
+      </c>
+      <c r="D150" s="33"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="33">
         <v>13379</v>
       </c>
       <c r="B151" s="33"/>
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
+      <c r="C151" s="33">
+        <v>13379</v>
+      </c>
+      <c r="D151" s="33"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="33">
         <v>8408</v>
       </c>
       <c r="B152" s="33"/>
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
+      <c r="C152" s="33">
+        <v>8408</v>
+      </c>
+      <c r="D152" s="33"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="33">
         <v>16644</v>
       </c>
       <c r="B153" s="33"/>
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
+      <c r="C153" s="33">
+        <v>16644</v>
+      </c>
+      <c r="D153" s="33"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="33">
         <v>10962</v>
       </c>
       <c r="B154" s="33"/>
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
+      <c r="C154" s="33">
+        <v>10962</v>
+      </c>
+      <c r="D154" s="33"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="33">
         <v>10739</v>
       </c>
       <c r="B155" s="33"/>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
+      <c r="C155" s="33">
+        <v>10739</v>
+      </c>
+      <c r="D155" s="33"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="33">
         <v>19109</v>
       </c>
       <c r="B156" s="33"/>
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
+      <c r="C156" s="33">
+        <v>19109</v>
+      </c>
+      <c r="D156" s="33"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="33">
         <v>15703</v>
       </c>
       <c r="B157" s="33"/>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
+      <c r="C157" s="33">
+        <v>15703</v>
+      </c>
+      <c r="D157" s="33"/>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="33">
         <v>17389</v>
       </c>
       <c r="B158" s="33"/>
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
+      <c r="C158" s="33">
+        <v>17389</v>
+      </c>
+      <c r="D158" s="33"/>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="33">
         <v>9421</v>
       </c>
       <c r="B159" s="33"/>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
+      <c r="C159" s="33">
+        <v>9421</v>
+      </c>
+      <c r="D159" s="33"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="33">
         <v>18374</v>
       </c>
       <c r="B160" s="33"/>
-      <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
+      <c r="C160" s="33">
+        <v>18374</v>
+      </c>
+      <c r="D160" s="33"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="33">
         <v>17667</v>
       </c>
       <c r="B161" s="33"/>
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
+      <c r="C161" s="33">
+        <v>17667</v>
+      </c>
+      <c r="D161" s="33"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="33">
         <v>14950</v>
       </c>
       <c r="B162" s="33"/>
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
+      <c r="C162" s="33">
+        <v>14950</v>
+      </c>
+      <c r="D162" s="33"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="33">
         <v>8128</v>
       </c>
       <c r="B163" s="33"/>
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
+      <c r="C163" s="33">
+        <v>8128</v>
+      </c>
+      <c r="D163" s="33"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="33">
         <v>15105</v>
       </c>
       <c r="B164" s="33"/>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
+      <c r="C164" s="33">
+        <v>15105</v>
+      </c>
+      <c r="D164" s="33"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="33">
         <v>17942</v>
       </c>
       <c r="B165" s="33"/>
-      <c r="C165" s="2"/>
-      <c r="D165" s="2"/>
+      <c r="C165" s="33">
+        <v>17942</v>
+      </c>
+      <c r="D165" s="33"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="33">
         <v>9420</v>
       </c>
       <c r="B166" s="33"/>
-      <c r="C166" s="2"/>
-      <c r="D166" s="2"/>
+      <c r="C166" s="33">
+        <v>9420</v>
+      </c>
+      <c r="D166" s="33"/>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="33">
         <v>10881</v>
       </c>
       <c r="B167" s="33"/>
-      <c r="C167" s="2"/>
-      <c r="D167" s="2"/>
+      <c r="C167" s="33">
+        <v>10881</v>
+      </c>
+      <c r="D167" s="33"/>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="33">
         <v>18443</v>
       </c>
       <c r="B168" s="33"/>
-      <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
+      <c r="C168" s="33">
+        <v>18443</v>
+      </c>
+      <c r="D168" s="33"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="33">
         <v>13026</v>
       </c>
       <c r="B169" s="33"/>
-      <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
+      <c r="C169" s="33">
+        <v>13026</v>
+      </c>
+      <c r="D169" s="33"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="33">
         <v>9608</v>
       </c>
       <c r="B170" s="33"/>
-      <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
+      <c r="C170" s="33">
+        <v>9608</v>
+      </c>
+      <c r="D170" s="33"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="33">
         <v>15620</v>
       </c>
       <c r="B171" s="33"/>
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
+      <c r="C171" s="33">
+        <v>15620</v>
+      </c>
+      <c r="D171" s="33"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="33">
         <v>16462</v>
       </c>
       <c r="B172" s="33"/>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
+      <c r="C172" s="33">
+        <v>16462</v>
+      </c>
+      <c r="D172" s="33"/>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="33">
         <v>18872</v>
       </c>
       <c r="B173" s="33"/>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
+      <c r="C173" s="33">
+        <v>18872</v>
+      </c>
+      <c r="D173" s="33"/>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="33">
         <v>15936</v>
       </c>
       <c r="B174" s="33"/>
-      <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
+      <c r="C174" s="33">
+        <v>15936</v>
+      </c>
+      <c r="D174" s="33"/>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="33">
         <v>14138</v>
       </c>
       <c r="B175" s="33"/>
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
+      <c r="C175" s="33">
+        <v>14138</v>
+      </c>
+      <c r="D175" s="33"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="33">
         <v>17139</v>
       </c>
       <c r="B176" s="33"/>
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
+      <c r="C176" s="33">
+        <v>17139</v>
+      </c>
+      <c r="D176" s="33"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="33">
         <v>18686</v>
       </c>
       <c r="B177" s="33"/>
-      <c r="C177" s="2"/>
-      <c r="D177" s="2"/>
+      <c r="C177" s="33">
+        <v>18686</v>
+      </c>
+      <c r="D177" s="33"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="33">
         <v>17377</v>
       </c>
       <c r="B178" s="33"/>
-      <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
+      <c r="C178" s="33">
+        <v>17377</v>
+      </c>
+      <c r="D178" s="33"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="33">
         <v>19631</v>
       </c>
       <c r="B179" s="33"/>
-      <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
+      <c r="C179" s="33">
+        <v>19631</v>
+      </c>
+      <c r="D179" s="33"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="33">
         <v>15677</v>
       </c>
       <c r="B180" s="33"/>
-      <c r="C180" s="2"/>
-      <c r="D180" s="2"/>
+      <c r="C180" s="33">
+        <v>15677</v>
+      </c>
+      <c r="D180" s="33"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="33">
         <v>14951</v>
       </c>
       <c r="B181" s="33"/>
-      <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
+      <c r="C181" s="33">
+        <v>14951</v>
+      </c>
+      <c r="D181" s="33"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="33">
         <v>18978</v>
       </c>
       <c r="B182" s="33"/>
-      <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
+      <c r="C182" s="33">
+        <v>18978</v>
+      </c>
+      <c r="D182" s="33"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="33">
         <v>19142</v>
       </c>
       <c r="B183" s="33"/>
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
+      <c r="C183" s="33">
+        <v>19142</v>
+      </c>
+      <c r="D183" s="33"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="33">
         <v>13500</v>
       </c>
       <c r="B184" s="33"/>
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
+      <c r="C184" s="33">
+        <v>13500</v>
+      </c>
+      <c r="D184" s="33"/>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="33">
         <v>15480</v>
       </c>
       <c r="B185" s="33"/>
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
+      <c r="C185" s="33">
+        <v>15480</v>
+      </c>
+      <c r="D185" s="33"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="33">
         <v>15255</v>
       </c>
       <c r="B186" s="33"/>
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
+      <c r="C186" s="33">
+        <v>15255</v>
+      </c>
+      <c r="D186" s="33"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="33">
         <v>12603</v>
       </c>
       <c r="B187" s="33"/>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
+      <c r="C187" s="33">
+        <v>12603</v>
+      </c>
+      <c r="D187" s="33"/>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="33">
         <v>19140</v>
       </c>
       <c r="B188" s="33"/>
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
+      <c r="C188" s="33">
+        <v>19140</v>
+      </c>
+      <c r="D188" s="33"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="33">
         <v>11549</v>
       </c>
       <c r="B189" s="33"/>
-      <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
+      <c r="C189" s="33">
+        <v>11549</v>
+      </c>
+      <c r="D189" s="33"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="33">
         <v>14567</v>
       </c>
       <c r="B190" s="33"/>
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
+      <c r="C190" s="33">
+        <v>14567</v>
+      </c>
+      <c r="D190" s="33"/>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="33">
         <v>13366</v>
       </c>
       <c r="B191" s="33"/>
-      <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
+      <c r="C191" s="33">
+        <v>13366</v>
+      </c>
+      <c r="D191" s="33"/>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="33">
         <v>9132</v>
       </c>
       <c r="B192" s="33"/>
-      <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
+      <c r="C192" s="33">
+        <v>9132</v>
+      </c>
+      <c r="D192" s="33"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="33">
         <v>21752</v>
       </c>
       <c r="B193" s="33"/>
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
+      <c r="C193" s="33">
+        <v>21752</v>
+      </c>
+      <c r="D193" s="33"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="33">
         <v>14631</v>
       </c>
       <c r="B194" s="33"/>
-      <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
+      <c r="C194" s="33">
+        <v>14631</v>
+      </c>
+      <c r="D194" s="33"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="33">
         <v>13698</v>
       </c>
       <c r="B195" s="33"/>
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
+      <c r="C195" s="33">
+        <v>13698</v>
+      </c>
+      <c r="D195" s="33"/>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="33">
         <v>11755</v>
       </c>
       <c r="B196" s="33"/>
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
+      <c r="C196" s="33">
+        <v>11755</v>
+      </c>
+      <c r="D196" s="33"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="33">
         <v>9145</v>
       </c>
       <c r="B197" s="33"/>
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
+      <c r="C197" s="33">
+        <v>9145</v>
+      </c>
+      <c r="D197" s="33"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="33">
         <v>10937</v>
       </c>
       <c r="B198" s="33"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
+      <c r="C198" s="33">
+        <v>10937</v>
+      </c>
+      <c r="D198" s="33"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="33">
         <v>18407</v>
       </c>
       <c r="B199" s="33"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
+      <c r="C199" s="33">
+        <v>18407</v>
+      </c>
+      <c r="D199" s="33"/>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="33">
         <v>10457</v>
       </c>
       <c r="B200" s="33"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
+      <c r="C200" s="33">
+        <v>10457</v>
+      </c>
+      <c r="D200" s="33"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="33">
         <v>14005</v>
       </c>
       <c r="B201" s="33"/>
-      <c r="C201" s="2"/>
-      <c r="D201" s="2"/>
+      <c r="C201" s="33">
+        <v>14005</v>
+      </c>
+      <c r="D201" s="33"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="33">
         <v>29658</v>
       </c>
       <c r="B202" s="33"/>
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
+      <c r="C202" s="33">
+        <v>26355</v>
+      </c>
+      <c r="D202" s="33"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="33">
         <v>17473</v>
       </c>
       <c r="B203" s="33"/>
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
+      <c r="C203" s="33">
+        <v>17473</v>
+      </c>
+      <c r="D203" s="33"/>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="33">
         <v>30258</v>
       </c>
       <c r="B204" s="33"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
+      <c r="C204" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D204" s="33"/>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="33">
         <v>10276</v>
       </c>
       <c r="B205" s="33"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
+      <c r="C205" s="33">
+        <v>10276</v>
+      </c>
+      <c r="D205" s="33"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="33">
         <v>11847</v>
       </c>
       <c r="B206" s="33"/>
-      <c r="C206" s="2"/>
-      <c r="D206" s="2"/>
+      <c r="C206" s="33">
+        <v>11847</v>
+      </c>
+      <c r="D206" s="33"/>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="33">
         <v>11374</v>
       </c>
       <c r="B207" s="33"/>
-      <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
+      <c r="C207" s="33">
+        <v>11374</v>
+      </c>
+      <c r="D207" s="33"/>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="33">
         <v>18467</v>
       </c>
       <c r="B208" s="33"/>
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
+      <c r="C208" s="33">
+        <v>18467</v>
+      </c>
+      <c r="D208" s="33"/>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="33">
         <v>11605</v>
       </c>
       <c r="B209" s="33"/>
-      <c r="C209" s="2"/>
-      <c r="D209" s="2"/>
+      <c r="C209" s="33">
+        <v>11605</v>
+      </c>
+      <c r="D209" s="33"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="33">
         <v>9914</v>
       </c>
       <c r="B210" s="33"/>
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
+      <c r="C210" s="33">
+        <v>9914</v>
+      </c>
+      <c r="D210" s="33"/>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="33">
         <v>15442</v>
       </c>
       <c r="B211" s="33"/>
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
+      <c r="C211" s="33">
+        <v>15442</v>
+      </c>
+      <c r="D211" s="33"/>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="33">
         <v>13500</v>
       </c>
       <c r="B212" s="33"/>
-      <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
+      <c r="C212" s="33">
+        <v>13500</v>
+      </c>
+      <c r="D212" s="33"/>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="33">
         <v>15514</v>
       </c>
       <c r="B213" s="33"/>
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
+      <c r="C213" s="33">
+        <v>15514</v>
+      </c>
+      <c r="D213" s="33"/>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="33">
         <v>16554</v>
       </c>
       <c r="B214" s="33"/>
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
+      <c r="C214" s="33">
+        <v>16554</v>
+      </c>
+      <c r="D214" s="33"/>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="33">
         <v>31483</v>
       </c>
       <c r="B215" s="33"/>
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
+      <c r="C215" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D215" s="33"/>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="33">
         <v>13408</v>
       </c>
       <c r="B216" s="33"/>
-      <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
+      <c r="C216" s="33">
+        <v>13408</v>
+      </c>
+      <c r="D216" s="33"/>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="33">
         <v>30478</v>
       </c>
       <c r="B217" s="33"/>
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
+      <c r="C217" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D217" s="33"/>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="33">
         <v>13500</v>
       </c>
       <c r="B218" s="33"/>
-      <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
+      <c r="C218" s="33">
+        <v>13500</v>
+      </c>
+      <c r="D218" s="33"/>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="33">
         <v>14300</v>
       </c>
       <c r="B219" s="33"/>
-      <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
+      <c r="C219" s="33">
+        <v>14300</v>
+      </c>
+      <c r="D219" s="33"/>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="33">
         <v>31178</v>
       </c>
       <c r="B220" s="33"/>
-      <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
+      <c r="C220" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D220" s="33"/>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="33">
         <v>8089</v>
       </c>
       <c r="B221" s="33"/>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
+      <c r="C221" s="33">
+        <v>8089</v>
+      </c>
+      <c r="D221" s="33"/>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="33">
         <v>18283</v>
       </c>
       <c r="B222" s="33"/>
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
+      <c r="C222" s="33">
+        <v>18283</v>
+      </c>
+      <c r="D222" s="33"/>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="33">
         <v>13217</v>
       </c>
       <c r="B223" s="33"/>
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
+      <c r="C223" s="33">
+        <v>13217</v>
+      </c>
+      <c r="D223" s="33"/>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="33">
         <v>8499</v>
       </c>
       <c r="B224" s="33"/>
-      <c r="C224" s="2"/>
-      <c r="D224" s="2"/>
+      <c r="C224" s="33">
+        <v>8499</v>
+      </c>
+      <c r="D224" s="33"/>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="33">
         <v>10707</v>
       </c>
       <c r="B225" s="33"/>
-      <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
+      <c r="C225" s="33">
+        <v>10707</v>
+      </c>
+      <c r="D225" s="33"/>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="33">
         <v>11174</v>
       </c>
       <c r="B226" s="33"/>
-      <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
+      <c r="C226" s="33">
+        <v>11174</v>
+      </c>
+      <c r="D226" s="33"/>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="33">
         <v>14447</v>
       </c>
       <c r="B227" s="33"/>
-      <c r="C227" s="2"/>
-      <c r="D227" s="2"/>
+      <c r="C227" s="33">
+        <v>14447</v>
+      </c>
+      <c r="D227" s="33"/>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="33">
         <v>11562</v>
       </c>
       <c r="B228" s="33"/>
-      <c r="C228" s="2"/>
-      <c r="D228" s="2"/>
+      <c r="C228" s="33">
+        <v>11562</v>
+      </c>
+      <c r="D228" s="33"/>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="33">
         <v>34444</v>
       </c>
       <c r="B229" s="33"/>
-      <c r="C229" s="2"/>
-      <c r="D229" s="2"/>
+      <c r="C229" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D229" s="33"/>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="33">
         <v>15663</v>
       </c>
       <c r="B230" s="33"/>
-      <c r="C230" s="2"/>
-      <c r="D230" s="2"/>
+      <c r="C230" s="33">
+        <v>15663</v>
+      </c>
+      <c r="D230" s="33"/>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="33">
         <v>13500</v>
       </c>
       <c r="B231" s="33"/>
-      <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
+      <c r="C231" s="33">
+        <v>13500</v>
+      </c>
+      <c r="D231" s="33"/>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="33">
         <v>8143</v>
       </c>
       <c r="B232" s="33"/>
-      <c r="C232" s="2"/>
-      <c r="D232" s="2"/>
+      <c r="C232" s="33">
+        <v>8143</v>
+      </c>
+      <c r="D232" s="33"/>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="33">
         <v>36214</v>
       </c>
       <c r="B233" s="33"/>
-      <c r="C233" s="2"/>
-      <c r="D233" s="2"/>
+      <c r="C233" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D233" s="33"/>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="33">
         <v>38437</v>
       </c>
       <c r="B234" s="33"/>
-      <c r="C234" s="2"/>
-      <c r="D234" s="2"/>
+      <c r="C234" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D234" s="33"/>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="33">
         <v>15133</v>
       </c>
       <c r="B235" s="33"/>
-      <c r="C235" s="2"/>
-      <c r="D235" s="2"/>
+      <c r="C235" s="33">
+        <v>15133</v>
+      </c>
+      <c r="D235" s="33"/>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="33">
         <v>16809</v>
       </c>
       <c r="B236" s="33"/>
-      <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
+      <c r="C236" s="33">
+        <v>16809</v>
+      </c>
+      <c r="D236" s="33"/>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="33">
         <v>8959</v>
       </c>
       <c r="B237" s="33"/>
-      <c r="C237" s="2"/>
-      <c r="D237" s="2"/>
+      <c r="C237" s="33">
+        <v>8959</v>
+      </c>
+      <c r="D237" s="33"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="33">
         <v>15003</v>
       </c>
       <c r="B238" s="33"/>
-      <c r="C238" s="2"/>
-      <c r="D238" s="2"/>
+      <c r="C238" s="33">
+        <v>15003</v>
+      </c>
+      <c r="D238" s="33"/>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="33">
         <v>13861</v>
       </c>
       <c r="B239" s="33"/>
-      <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
+      <c r="C239" s="33">
+        <v>13861</v>
+      </c>
+      <c r="D239" s="33"/>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="33">
         <v>10178</v>
       </c>
       <c r="B240" s="33"/>
-      <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
+      <c r="C240" s="33">
+        <v>10178</v>
+      </c>
+      <c r="D240" s="33"/>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="33">
         <v>12606</v>
       </c>
       <c r="B241" s="33"/>
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
+      <c r="C241" s="33">
+        <v>12606</v>
+      </c>
+      <c r="D241" s="33"/>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="33">
         <v>34240</v>
       </c>
       <c r="B242" s="33"/>
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
+      <c r="C242" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D242" s="33"/>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="33">
         <v>38142</v>
       </c>
       <c r="B243" s="33"/>
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
+      <c r="C243" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D243" s="33"/>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="33">
         <v>13496</v>
       </c>
       <c r="B244" s="33"/>
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
+      <c r="C244" s="33">
+        <v>13496</v>
+      </c>
+      <c r="D244" s="33"/>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="33">
         <v>12710</v>
       </c>
       <c r="B245" s="33"/>
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
+      <c r="C245" s="33">
+        <v>12710</v>
+      </c>
+      <c r="D245" s="33"/>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="33">
         <v>10745</v>
       </c>
       <c r="B246" s="33"/>
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
+      <c r="C246" s="33">
+        <v>10745</v>
+      </c>
+      <c r="D246" s="33"/>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="33">
         <v>19085</v>
       </c>
       <c r="B247" s="33"/>
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
+      <c r="C247" s="33">
+        <v>19085</v>
+      </c>
+      <c r="D247" s="33"/>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="33">
         <v>18875</v>
       </c>
       <c r="B248" s="33"/>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
+      <c r="C248" s="33">
+        <v>18875</v>
+      </c>
+      <c r="D248" s="33"/>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="33">
         <v>17153</v>
       </c>
       <c r="B249" s="33"/>
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
+      <c r="C249" s="33">
+        <v>17153</v>
+      </c>
+      <c r="D249" s="33"/>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="33">
         <v>9654</v>
       </c>
       <c r="B250" s="33"/>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
+      <c r="C250" s="33">
+        <v>9654</v>
+      </c>
+      <c r="D250" s="33"/>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="33">
         <v>12875</v>
       </c>
       <c r="B251" s="33"/>
-      <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
+      <c r="C251" s="33">
+        <v>12875</v>
+      </c>
+      <c r="D251" s="33"/>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="33">
         <v>12297</v>
       </c>
       <c r="B252" s="33"/>
-      <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
+      <c r="C252" s="33">
+        <v>12297</v>
+      </c>
+      <c r="D252" s="33"/>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="33">
         <v>31525</v>
       </c>
       <c r="B253" s="33"/>
-      <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
+      <c r="C253" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D253" s="33"/>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="33">
         <v>18494</v>
       </c>
       <c r="B254" s="33"/>
-      <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
+      <c r="C254" s="33">
+        <v>18494</v>
+      </c>
+      <c r="D254" s="33"/>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="33">
         <v>32874</v>
       </c>
       <c r="B255" s="33"/>
-      <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
+      <c r="C255" s="61">
+        <v>26355</v>
+      </c>
+      <c r="D255" s="33"/>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="33">
         <v>15016</v>
       </c>
       <c r="B256" s="33"/>
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
+      <c r="C256" s="33">
+        <v>15016</v>
+      </c>
+      <c r="D256" s="33"/>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="33">
         <v>18377</v>
       </c>
       <c r="B257" s="33"/>
-      <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
+      <c r="C257" s="33">
+        <v>18377</v>
+      </c>
+      <c r="D257" s="33"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="33">
         <v>10627</v>
       </c>
       <c r="B258" s="33"/>
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
+      <c r="C258" s="33">
+        <v>10627</v>
+      </c>
+      <c r="D258" s="33"/>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="33">
         <v>13986</v>
       </c>
       <c r="B259" s="33"/>
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
+      <c r="C259" s="33">
+        <v>13986</v>
+      </c>
+      <c r="D259" s="33"/>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="33">
         <v>12142</v>
       </c>
       <c r="B260" s="33"/>
-      <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
+      <c r="C260" s="33">
+        <v>12142</v>
+      </c>
+      <c r="D260" s="33"/>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="33">
         <v>19482</v>
       </c>
       <c r="B261" s="33"/>
-      <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
+      <c r="C261" s="33">
+        <v>19482</v>
+      </c>
+      <c r="D261" s="33"/>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="33">
         <v>11684</v>
       </c>
       <c r="B262" s="33"/>
-      <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
+      <c r="C262" s="33">
+        <v>11684</v>
+      </c>
+      <c r="D262" s="33"/>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="33">
         <v>16113</v>
       </c>
       <c r="B263" s="33"/>
-      <c r="C263" s="2"/>
-      <c r="D263" s="2"/>
+      <c r="C263" s="33">
+        <v>16113</v>
+      </c>
+      <c r="D263" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -32079,6 +33661,18 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="F1:F2"/>
   </mergeCells>
+  <conditionalFormatting sqref="C4:C263">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="notBetween">
+      <formula>2290</formula>
+      <formula>26355</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D108">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="notBetween">
+      <formula>12468</formula>
+      <formula>42892</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -32093,7 +33687,9 @@
     <col min="3" max="3" width="10.77734375" customWidth="1"/>
     <col min="5" max="5" width="10.5546875" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" customWidth="1"/>
     <col min="15" max="15" width="14.5546875" customWidth="1"/>
     <col min="16" max="16" width="10.109375" customWidth="1"/>
     <col min="17" max="17" width="12.77734375" customWidth="1"/>
@@ -32206,9 +33802,18 @@
       <c r="H3" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="I3" s="23">
+        <f>QUARTILE(A4:A122,1)</f>
+        <v>1234</v>
+      </c>
+      <c r="J3" s="18">
+        <f>QUARTILE(B4:B61,1)</f>
+        <v>1546</v>
+      </c>
+      <c r="K3" s="18">
+        <f>QUARTILE(C4:C191,1)</f>
+        <v>1473.75</v>
+      </c>
       <c r="O3" s="8" t="s">
         <v>29</v>
       </c>
@@ -32241,12 +33846,30 @@
       <c r="C4" s="33">
         <v>2564</v>
       </c>
+      <c r="D4" s="33">
+        <v>1708</v>
+      </c>
+      <c r="E4" s="33">
+        <v>2661</v>
+      </c>
+      <c r="F4" s="33">
+        <v>2564</v>
+      </c>
       <c r="H4" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
+      <c r="I4" s="23">
+        <f>QUARTILE(A4:A122,3)</f>
+        <v>3041</v>
+      </c>
+      <c r="J4" s="18">
+        <f>QUARTILE(B4:B61,3)</f>
+        <v>2789.25</v>
+      </c>
+      <c r="K4" s="18">
+        <f>QUARTILE(C4:C191,3)</f>
+        <v>3100.75</v>
+      </c>
       <c r="O4" s="8" t="s">
         <v>30</v>
       </c>
@@ -32279,12 +33902,30 @@
       <c r="C5" s="33">
         <v>2463</v>
       </c>
+      <c r="D5" s="33">
+        <v>1776</v>
+      </c>
+      <c r="E5" s="33">
+        <v>1333</v>
+      </c>
+      <c r="F5" s="33">
+        <v>2463</v>
+      </c>
       <c r="H5" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
+      <c r="I5" s="19">
+        <f>I4-I3</f>
+        <v>1807</v>
+      </c>
+      <c r="J5" s="19">
+        <f>J4-J3</f>
+        <v>1243.25</v>
+      </c>
+      <c r="K5" s="19">
+        <f>K4-K3</f>
+        <v>1627</v>
+      </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
       <c r="O5" s="8" t="s">
@@ -32319,12 +33960,30 @@
       <c r="C6" s="33">
         <v>3007</v>
       </c>
+      <c r="D6" s="33">
+        <v>2131</v>
+      </c>
+      <c r="E6" s="33">
+        <v>3897</v>
+      </c>
+      <c r="F6" s="33">
+        <v>3007</v>
+      </c>
       <c r="H6" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
+      <c r="I6" s="19">
+        <f>I3-1.5*I5</f>
+        <v>-1476.5</v>
+      </c>
+      <c r="J6" s="19">
+        <f>J3-1.5*J5</f>
+        <v>-318.875</v>
+      </c>
+      <c r="K6" s="19">
+        <f>K3-1.5*K5</f>
+        <v>-966.75</v>
+      </c>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
     </row>
@@ -32338,12 +33997,30 @@
       <c r="C7" s="33">
         <v>2157</v>
       </c>
+      <c r="D7" s="33">
+        <v>3135</v>
+      </c>
+      <c r="E7" s="33">
+        <v>3566</v>
+      </c>
+      <c r="F7" s="33">
+        <v>2157</v>
+      </c>
       <c r="H7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
+      <c r="I7" s="19">
+        <f>I4+1.5*I5</f>
+        <v>5751.5</v>
+      </c>
+      <c r="J7" s="19">
+        <f>J4+1.5*J5</f>
+        <v>4654.125</v>
+      </c>
+      <c r="K7" s="19">
+        <f>K4+1.5*K5</f>
+        <v>5541.25</v>
+      </c>
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
       <c r="T7" s="34"/>
@@ -32361,6 +34038,15 @@
       <c r="C8" s="33">
         <v>927</v>
       </c>
+      <c r="D8" s="33">
+        <v>748</v>
+      </c>
+      <c r="E8" s="33">
+        <v>2105</v>
+      </c>
+      <c r="F8" s="33">
+        <v>927</v>
+      </c>
       <c r="T8" s="34"/>
       <c r="U8" s="34"/>
       <c r="V8" s="34"/>
@@ -32376,6 +34062,15 @@
       <c r="C9" s="33">
         <v>1922</v>
       </c>
+      <c r="D9" s="33">
+        <v>1701</v>
+      </c>
+      <c r="E9" s="33">
+        <v>1059</v>
+      </c>
+      <c r="F9" s="33">
+        <v>1922</v>
+      </c>
       <c r="T9" s="34"/>
       <c r="U9" s="34"/>
       <c r="V9" s="34"/>
@@ -32391,6 +34086,15 @@
       <c r="C10" s="33">
         <v>1561</v>
       </c>
+      <c r="D10" s="33">
+        <v>2328</v>
+      </c>
+      <c r="E10" s="33">
+        <v>2099</v>
+      </c>
+      <c r="F10" s="33">
+        <v>1561</v>
+      </c>
       <c r="T10" s="34"/>
       <c r="U10" s="34"/>
       <c r="V10" s="34"/>
@@ -32406,6 +34110,15 @@
       <c r="C11" s="33">
         <v>2978</v>
       </c>
+      <c r="D11" s="33">
+        <v>1793</v>
+      </c>
+      <c r="E11" s="33">
+        <v>622</v>
+      </c>
+      <c r="F11" s="33">
+        <v>2978</v>
+      </c>
       <c r="T11" s="34"/>
       <c r="U11" s="34"/>
       <c r="V11" s="34"/>
@@ -32421,6 +34134,15 @@
       <c r="C12" s="33">
         <v>3738</v>
       </c>
+      <c r="D12" s="33">
+        <v>1890</v>
+      </c>
+      <c r="E12" s="33">
+        <v>2357</v>
+      </c>
+      <c r="F12" s="33">
+        <v>3738</v>
+      </c>
       <c r="T12" s="34"/>
       <c r="U12" s="34"/>
       <c r="V12" s="34"/>
@@ -32436,6 +34158,15 @@
       <c r="C13" s="33">
         <v>3490</v>
       </c>
+      <c r="D13" s="33">
+        <v>3123</v>
+      </c>
+      <c r="E13" s="33">
+        <v>2088</v>
+      </c>
+      <c r="F13" s="33">
+        <v>3490</v>
+      </c>
       <c r="T13" s="34"/>
       <c r="U13" s="34"/>
       <c r="V13" s="34"/>
@@ -32451,6 +34182,15 @@
       <c r="C14" s="33">
         <v>593</v>
       </c>
+      <c r="D14" s="33">
+        <v>534</v>
+      </c>
+      <c r="E14" s="33">
+        <v>3996</v>
+      </c>
+      <c r="F14" s="33">
+        <v>593</v>
+      </c>
       <c r="T14" s="34"/>
       <c r="U14" s="34"/>
       <c r="V14" s="34"/>
@@ -32466,6 +34206,15 @@
       <c r="C15" s="33">
         <v>1708</v>
       </c>
+      <c r="D15" s="33">
+        <v>1002</v>
+      </c>
+      <c r="E15" s="33">
+        <v>1901</v>
+      </c>
+      <c r="F15" s="33">
+        <v>1708</v>
+      </c>
       <c r="T15" s="34"/>
       <c r="U15" s="34"/>
       <c r="V15" s="34"/>
@@ -32481,6 +34230,15 @@
       <c r="C16" s="33">
         <v>3816</v>
       </c>
+      <c r="D16" s="33">
+        <v>885</v>
+      </c>
+      <c r="E16" s="33">
+        <v>2787</v>
+      </c>
+      <c r="F16" s="33">
+        <v>3816</v>
+      </c>
       <c r="T16" s="34"/>
       <c r="U16" s="34"/>
       <c r="V16" s="34"/>
@@ -32496,6 +34254,15 @@
       <c r="C17" s="33">
         <v>2570</v>
       </c>
+      <c r="D17" s="33">
+        <v>2935</v>
+      </c>
+      <c r="E17" s="33">
+        <v>623</v>
+      </c>
+      <c r="F17" s="33">
+        <v>2570</v>
+      </c>
       <c r="T17" s="34"/>
       <c r="U17" s="34"/>
       <c r="V17" s="34"/>
@@ -32511,6 +34278,15 @@
       <c r="C18" s="33">
         <v>3134</v>
       </c>
+      <c r="D18" s="33">
+        <v>1300</v>
+      </c>
+      <c r="E18" s="33">
+        <v>1102</v>
+      </c>
+      <c r="F18" s="33">
+        <v>3134</v>
+      </c>
       <c r="T18" s="34"/>
       <c r="U18" s="34"/>
       <c r="V18" s="34"/>
@@ -32526,6 +34302,15 @@
       <c r="C19" s="33">
         <v>3978</v>
       </c>
+      <c r="D19" s="33">
+        <v>2527</v>
+      </c>
+      <c r="E19" s="33">
+        <v>2215</v>
+      </c>
+      <c r="F19" s="33">
+        <v>3978</v>
+      </c>
       <c r="T19" s="34"/>
       <c r="U19" s="34"/>
       <c r="V19" s="34"/>
@@ -32541,6 +34326,15 @@
       <c r="C20" s="33">
         <v>1329</v>
       </c>
+      <c r="D20" s="33">
+        <v>3176</v>
+      </c>
+      <c r="E20" s="33">
+        <v>512</v>
+      </c>
+      <c r="F20" s="33">
+        <v>1329</v>
+      </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
@@ -32552,6 +34346,15 @@
       <c r="C21" s="33">
         <v>1301</v>
       </c>
+      <c r="D21" s="33">
+        <v>3683</v>
+      </c>
+      <c r="E21" s="33">
+        <v>2305</v>
+      </c>
+      <c r="F21" s="33">
+        <v>1301</v>
+      </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="33">
@@ -32563,6 +34366,15 @@
       <c r="C22" s="33">
         <v>3081</v>
       </c>
+      <c r="D22" s="33">
+        <v>905</v>
+      </c>
+      <c r="E22" s="33">
+        <v>1600</v>
+      </c>
+      <c r="F22" s="33">
+        <v>3081</v>
+      </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
@@ -32574,6 +34386,15 @@
       <c r="C23" s="33">
         <v>695</v>
       </c>
+      <c r="D23" s="33">
+        <v>1394</v>
+      </c>
+      <c r="E23" s="33">
+        <v>1136</v>
+      </c>
+      <c r="F23" s="33">
+        <v>695</v>
+      </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="33">
@@ -32585,6 +34406,15 @@
       <c r="C24" s="33">
         <v>3196</v>
       </c>
+      <c r="D24" s="33">
+        <v>2027</v>
+      </c>
+      <c r="E24" s="33">
+        <v>2141</v>
+      </c>
+      <c r="F24" s="33">
+        <v>3196</v>
+      </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
@@ -32596,6 +34426,15 @@
       <c r="C25" s="33">
         <v>3268</v>
       </c>
+      <c r="D25" s="33">
+        <v>3796</v>
+      </c>
+      <c r="E25" s="33">
+        <v>3425</v>
+      </c>
+      <c r="F25" s="33">
+        <v>3268</v>
+      </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
@@ -32607,6 +34446,15 @@
       <c r="C26" s="33">
         <v>3891</v>
       </c>
+      <c r="D26" s="33">
+        <v>2006</v>
+      </c>
+      <c r="E26" s="33">
+        <v>3693</v>
+      </c>
+      <c r="F26" s="33">
+        <v>3891</v>
+      </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
@@ -32618,6 +34466,15 @@
       <c r="C27" s="33">
         <v>1387</v>
       </c>
+      <c r="D27" s="33">
+        <v>2215</v>
+      </c>
+      <c r="E27" s="33">
+        <v>928</v>
+      </c>
+      <c r="F27" s="33">
+        <v>1387</v>
+      </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
@@ -32629,6 +34486,15 @@
       <c r="C28" s="33">
         <v>853</v>
       </c>
+      <c r="D28" s="33">
+        <v>2210</v>
+      </c>
+      <c r="E28" s="33">
+        <v>2214</v>
+      </c>
+      <c r="F28" s="33">
+        <v>853</v>
+      </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
@@ -32640,6 +34506,15 @@
       <c r="C29" s="33">
         <v>3353</v>
       </c>
+      <c r="D29" s="33">
+        <v>744</v>
+      </c>
+      <c r="E29" s="33">
+        <v>1710</v>
+      </c>
+      <c r="F29" s="33">
+        <v>3353</v>
+      </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
@@ -32651,6 +34526,15 @@
       <c r="C30" s="33">
         <v>877</v>
       </c>
+      <c r="D30" s="33">
+        <v>1240</v>
+      </c>
+      <c r="E30" s="33">
+        <v>3655</v>
+      </c>
+      <c r="F30" s="33">
+        <v>877</v>
+      </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
@@ -32662,6 +34546,15 @@
       <c r="C31" s="33">
         <v>910</v>
       </c>
+      <c r="D31" s="33">
+        <v>547</v>
+      </c>
+      <c r="E31" s="33">
+        <v>3498</v>
+      </c>
+      <c r="F31" s="33">
+        <v>910</v>
+      </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
@@ -32673,8 +34566,17 @@
       <c r="C32" s="33">
         <v>2283</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" s="33">
+        <v>2418</v>
+      </c>
+      <c r="E32" s="33">
+        <v>786</v>
+      </c>
+      <c r="F32" s="33">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>1784</v>
       </c>
@@ -32684,8 +34586,17 @@
       <c r="C33" s="33">
         <v>827</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" s="33">
+        <v>1784</v>
+      </c>
+      <c r="E33" s="33">
+        <v>3285</v>
+      </c>
+      <c r="F33" s="33">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="33">
         <v>2901</v>
       </c>
@@ -32695,8 +34606,17 @@
       <c r="C34" s="33">
         <v>3342</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" s="33">
+        <v>2901</v>
+      </c>
+      <c r="E34" s="33">
+        <v>3351</v>
+      </c>
+      <c r="F34" s="33">
+        <v>3342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>3568</v>
       </c>
@@ -32706,8 +34626,17 @@
       <c r="C35" s="33">
         <v>1222</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" s="33">
+        <v>3568</v>
+      </c>
+      <c r="E35" s="33">
+        <v>2746</v>
+      </c>
+      <c r="F35" s="33">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="33">
         <v>2210</v>
       </c>
@@ -32717,8 +34646,17 @@
       <c r="C36" s="33">
         <v>665</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" s="33">
+        <v>2210</v>
+      </c>
+      <c r="E36" s="33">
+        <v>2663</v>
+      </c>
+      <c r="F36" s="33">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>3118</v>
       </c>
@@ -32728,8 +34666,17 @@
       <c r="C37" s="33">
         <v>3598</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" s="33">
+        <v>3118</v>
+      </c>
+      <c r="E37" s="33">
+        <v>1673</v>
+      </c>
+      <c r="F37" s="33">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="33">
         <v>540</v>
       </c>
@@ -32739,8 +34686,17 @@
       <c r="C38" s="33">
         <v>3463</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" s="33">
+        <v>540</v>
+      </c>
+      <c r="E38" s="33">
+        <v>1613</v>
+      </c>
+      <c r="F38" s="33">
+        <v>3463</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
         <v>3409</v>
       </c>
@@ -32750,8 +34706,17 @@
       <c r="C39" s="33">
         <v>2694</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" s="33">
+        <v>3409</v>
+      </c>
+      <c r="E39" s="33">
+        <v>1163</v>
+      </c>
+      <c r="F39" s="33">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="33">
         <v>2442</v>
       </c>
@@ -32761,8 +34726,17 @@
       <c r="C40" s="33">
         <v>3829</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" s="33">
+        <v>2442</v>
+      </c>
+      <c r="E40" s="33">
+        <v>896</v>
+      </c>
+      <c r="F40" s="33">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>3667</v>
       </c>
@@ -32772,8 +34746,17 @@
       <c r="C41" s="33">
         <v>2866</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" s="33">
+        <v>3667</v>
+      </c>
+      <c r="E41" s="33">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="33">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="33">
         <v>2662</v>
       </c>
@@ -32783,8 +34766,17 @@
       <c r="C42" s="33">
         <v>3430</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" s="33">
+        <v>2662</v>
+      </c>
+      <c r="E42" s="33">
+        <v>2819</v>
+      </c>
+      <c r="F42" s="33">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="33">
         <v>2863</v>
       </c>
@@ -32794,8 +34786,17 @@
       <c r="C43" s="33">
         <v>676</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" s="33">
+        <v>2863</v>
+      </c>
+      <c r="E43" s="33">
+        <v>2210</v>
+      </c>
+      <c r="F43" s="33">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
         <v>2879</v>
       </c>
@@ -32805,8 +34806,17 @@
       <c r="C44" s="33">
         <v>1514</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" s="33">
+        <v>2879</v>
+      </c>
+      <c r="E44" s="33">
+        <v>2133</v>
+      </c>
+      <c r="F44" s="33">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="33">
         <v>918</v>
       </c>
@@ -32816,8 +34826,17 @@
       <c r="C45" s="33">
         <v>3194</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" s="33">
+        <v>918</v>
+      </c>
+      <c r="E45" s="33">
+        <v>3959</v>
+      </c>
+      <c r="F45" s="33">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="33">
         <v>3000</v>
       </c>
@@ -32827,8 +34846,17 @@
       <c r="C46" s="33">
         <v>1658</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" s="33">
+        <v>3000</v>
+      </c>
+      <c r="E46" s="33">
+        <v>944</v>
+      </c>
+      <c r="F46" s="33">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="33">
         <v>1279</v>
       </c>
@@ -32838,8 +34866,17 @@
       <c r="C47" s="33">
         <v>3332</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" s="33">
+        <v>1279</v>
+      </c>
+      <c r="E47" s="33">
+        <v>2099</v>
+      </c>
+      <c r="F47" s="33">
+        <v>3332</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="33">
         <v>1531</v>
       </c>
@@ -32849,8 +34886,17 @@
       <c r="C48" s="33">
         <v>2137</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" s="33">
+        <v>1531</v>
+      </c>
+      <c r="E48" s="33">
+        <v>1684</v>
+      </c>
+      <c r="F48" s="33">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="33">
         <v>1330</v>
       </c>
@@ -32860,8 +34906,17 @@
       <c r="C49" s="33">
         <v>3781</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" s="33">
+        <v>1330</v>
+      </c>
+      <c r="E49" s="33">
+        <v>1405</v>
+      </c>
+      <c r="F49" s="33">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="33">
         <v>742</v>
       </c>
@@ -32871,8 +34926,17 @@
       <c r="C50" s="33">
         <v>2380</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" s="33">
+        <v>742</v>
+      </c>
+      <c r="E50" s="33">
+        <v>2207</v>
+      </c>
+      <c r="F50" s="33">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="33">
         <v>2173</v>
       </c>
@@ -32882,8 +34946,17 @@
       <c r="C51" s="33">
         <v>1274</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" s="33">
+        <v>2173</v>
+      </c>
+      <c r="E51" s="33">
+        <v>1528</v>
+      </c>
+      <c r="F51" s="33">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="33">
         <v>2931</v>
       </c>
@@ -32893,8 +34966,17 @@
       <c r="C52" s="33">
         <v>3432</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" s="33">
+        <v>2931</v>
+      </c>
+      <c r="E52" s="33">
+        <v>1784</v>
+      </c>
+      <c r="F52" s="33">
+        <v>3432</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="33">
         <v>3399</v>
       </c>
@@ -32904,8 +34986,17 @@
       <c r="C53" s="33">
         <v>2887</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" s="33">
+        <v>3399</v>
+      </c>
+      <c r="E53" s="33">
+        <v>2790</v>
+      </c>
+      <c r="F53" s="33">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="33">
         <v>815</v>
       </c>
@@ -32915,8 +35006,17 @@
       <c r="C54" s="33">
         <v>3883</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" s="33">
+        <v>815</v>
+      </c>
+      <c r="E54" s="33">
+        <v>2387</v>
+      </c>
+      <c r="F54" s="33">
+        <v>3883</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="33">
         <v>1022</v>
       </c>
@@ -32926,8 +35026,17 @@
       <c r="C55" s="33">
         <v>3270</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" s="33">
+        <v>1022</v>
+      </c>
+      <c r="E55" s="33">
+        <v>1915</v>
+      </c>
+      <c r="F55" s="33">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="33">
         <v>925</v>
       </c>
@@ -32937,8 +35046,17 @@
       <c r="C56" s="33">
         <v>822</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" s="33">
+        <v>925</v>
+      </c>
+      <c r="E56" s="33">
+        <v>3849</v>
+      </c>
+      <c r="F56" s="33">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="33">
         <v>3082</v>
       </c>
@@ -32948,8 +35066,17 @@
       <c r="C57" s="33">
         <v>3066</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57" s="33">
+        <v>3082</v>
+      </c>
+      <c r="E57" s="33">
+        <v>1678</v>
+      </c>
+      <c r="F57" s="33">
+        <v>3066</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="33">
         <v>3150</v>
       </c>
@@ -32959,8 +35086,17 @@
       <c r="C58" s="33">
         <v>623</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58" s="33">
+        <v>3150</v>
+      </c>
+      <c r="E58" s="33">
+        <v>2099</v>
+      </c>
+      <c r="F58" s="33">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="33">
         <v>2539</v>
       </c>
@@ -32970,8 +35106,17 @@
       <c r="C59" s="33">
         <v>3592</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59" s="33">
+        <v>2539</v>
+      </c>
+      <c r="E59" s="33">
+        <v>3109</v>
+      </c>
+      <c r="F59" s="33">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="33">
         <v>1007</v>
       </c>
@@ -32981,8 +35126,17 @@
       <c r="C60" s="33">
         <v>3753</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60" s="33">
+        <v>1007</v>
+      </c>
+      <c r="E60" s="33">
+        <v>2099</v>
+      </c>
+      <c r="F60" s="33">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="33">
         <v>972</v>
       </c>
@@ -32992,8 +35146,17 @@
       <c r="C61" s="33">
         <v>559</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61" s="33">
+        <v>972</v>
+      </c>
+      <c r="E61" s="33">
+        <v>3259</v>
+      </c>
+      <c r="F61" s="33">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="33">
         <v>3170</v>
       </c>
@@ -33001,8 +35164,15 @@
       <c r="C62" s="33">
         <v>2626</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62" s="33">
+        <v>3170</v>
+      </c>
+      <c r="E62" s="33"/>
+      <c r="F62" s="33">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="33">
         <v>2650</v>
       </c>
@@ -33010,8 +35180,15 @@
       <c r="C63" s="33">
         <v>2463</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63" s="33">
+        <v>2650</v>
+      </c>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="33">
         <v>3954</v>
       </c>
@@ -33019,8 +35196,15 @@
       <c r="C64" s="33">
         <v>532</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64" s="33">
+        <v>3954</v>
+      </c>
+      <c r="E64" s="33"/>
+      <c r="F64" s="33">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="33">
         <v>2577</v>
       </c>
@@ -33028,8 +35212,15 @@
       <c r="C65" s="33">
         <v>3001</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65" s="33">
+        <v>2577</v>
+      </c>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="33">
         <v>2498</v>
       </c>
@@ -33037,8 +35228,15 @@
       <c r="C66" s="33">
         <v>3575</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66" s="33">
+        <v>2498</v>
+      </c>
+      <c r="E66" s="33"/>
+      <c r="F66" s="33">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="33">
         <v>1121</v>
       </c>
@@ -33046,8 +35244,15 @@
       <c r="C67" s="33">
         <v>1828</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67" s="33">
+        <v>1121</v>
+      </c>
+      <c r="E67" s="33"/>
+      <c r="F67" s="33">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="33">
         <v>3402</v>
       </c>
@@ -33055,8 +35260,15 @@
       <c r="C68" s="33">
         <v>1486</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68" s="33">
+        <v>3402</v>
+      </c>
+      <c r="E68" s="33"/>
+      <c r="F68" s="33">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="33">
         <v>3477</v>
       </c>
@@ -33064,8 +35276,15 @@
       <c r="C69" s="33">
         <v>2404</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69" s="33">
+        <v>3477</v>
+      </c>
+      <c r="E69" s="33"/>
+      <c r="F69" s="33">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="33">
         <v>1243</v>
       </c>
@@ -33073,8 +35292,15 @@
       <c r="C70" s="33">
         <v>3930</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70" s="33">
+        <v>1243</v>
+      </c>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="33">
         <v>1819</v>
       </c>
@@ -33082,8 +35308,15 @@
       <c r="C71" s="33">
         <v>3391</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D71" s="33">
+        <v>1819</v>
+      </c>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="33">
         <v>977</v>
       </c>
@@ -33091,8 +35324,15 @@
       <c r="C72" s="33">
         <v>1440</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D72" s="33">
+        <v>977</v>
+      </c>
+      <c r="E72" s="33"/>
+      <c r="F72" s="33">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="33">
         <v>1904</v>
       </c>
@@ -33100,8 +35340,15 @@
       <c r="C73" s="33">
         <v>2882</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D73" s="33">
+        <v>1904</v>
+      </c>
+      <c r="E73" s="33"/>
+      <c r="F73" s="33">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="33">
         <v>3645</v>
       </c>
@@ -33109,8 +35356,15 @@
       <c r="C74" s="33">
         <v>2985</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D74" s="33">
+        <v>3645</v>
+      </c>
+      <c r="E74" s="33"/>
+      <c r="F74" s="33">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="33">
         <v>3934</v>
       </c>
@@ -33118,8 +35372,15 @@
       <c r="C75" s="33">
         <v>3092</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D75" s="33">
+        <v>3934</v>
+      </c>
+      <c r="E75" s="33"/>
+      <c r="F75" s="33">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="33">
         <v>2281</v>
       </c>
@@ -33127,8 +35388,15 @@
       <c r="C76" s="33">
         <v>3898</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D76" s="33">
+        <v>2281</v>
+      </c>
+      <c r="E76" s="33"/>
+      <c r="F76" s="33">
+        <v>3898</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="33">
         <v>2820</v>
       </c>
@@ -33136,8 +35404,15 @@
       <c r="C77" s="33">
         <v>502</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D77" s="33">
+        <v>2820</v>
+      </c>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="33">
         <v>1156</v>
       </c>
@@ -33145,8 +35420,15 @@
       <c r="C78" s="33">
         <v>2215</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D78" s="33">
+        <v>1156</v>
+      </c>
+      <c r="E78" s="33"/>
+      <c r="F78" s="33">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="33">
         <v>2718</v>
       </c>
@@ -33154,8 +35436,15 @@
       <c r="C79" s="33">
         <v>1338</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D79" s="33">
+        <v>2718</v>
+      </c>
+      <c r="E79" s="33"/>
+      <c r="F79" s="33">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="33">
         <v>1678</v>
       </c>
@@ -33163,8 +35452,15 @@
       <c r="C80" s="33">
         <v>2434</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80" s="33">
+        <v>1678</v>
+      </c>
+      <c r="E80" s="33"/>
+      <c r="F80" s="33">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="33">
         <v>3299</v>
       </c>
@@ -33172,8 +35468,15 @@
       <c r="C81" s="33">
         <v>3452</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81" s="33">
+        <v>3299</v>
+      </c>
+      <c r="E81" s="33"/>
+      <c r="F81" s="33">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="33">
         <v>2574</v>
       </c>
@@ -33181,8 +35484,15 @@
       <c r="C82" s="33">
         <v>891</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82" s="33">
+        <v>2574</v>
+      </c>
+      <c r="E82" s="33"/>
+      <c r="F82" s="33">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="33">
         <v>2330</v>
       </c>
@@ -33190,8 +35500,15 @@
       <c r="C83" s="33">
         <v>2463</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83" s="33">
+        <v>2330</v>
+      </c>
+      <c r="E83" s="33"/>
+      <c r="F83" s="33">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="33">
         <v>2755</v>
       </c>
@@ -33199,8 +35516,15 @@
       <c r="C84" s="33">
         <v>2534</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84" s="33">
+        <v>2755</v>
+      </c>
+      <c r="E84" s="33"/>
+      <c r="F84" s="33">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="33">
         <v>1150</v>
       </c>
@@ -33208,8 +35532,15 @@
       <c r="C85" s="33">
         <v>2377</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85" s="33">
+        <v>1150</v>
+      </c>
+      <c r="E85" s="33"/>
+      <c r="F85" s="33">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="33">
         <v>3251</v>
       </c>
@@ -33217,8 +35548,15 @@
       <c r="C86" s="33">
         <v>2925</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86" s="33">
+        <v>3251</v>
+      </c>
+      <c r="E86" s="33"/>
+      <c r="F86" s="33">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="33">
         <v>1767</v>
       </c>
@@ -33226,8 +35564,15 @@
       <c r="C87" s="33">
         <v>3739</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87" s="33">
+        <v>1767</v>
+      </c>
+      <c r="E87" s="33"/>
+      <c r="F87" s="33">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="33">
         <v>3213</v>
       </c>
@@ -33235,8 +35580,15 @@
       <c r="C88" s="33">
         <v>824</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88" s="33">
+        <v>3213</v>
+      </c>
+      <c r="E88" s="33"/>
+      <c r="F88" s="33">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="33">
         <v>3944</v>
       </c>
@@ -33244,8 +35596,15 @@
       <c r="C89" s="33">
         <v>2016</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89" s="33">
+        <v>3944</v>
+      </c>
+      <c r="E89" s="33"/>
+      <c r="F89" s="33">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="33">
         <v>3718</v>
       </c>
@@ -33253,8 +35612,15 @@
       <c r="C90" s="33">
         <v>1012</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90" s="33">
+        <v>3718</v>
+      </c>
+      <c r="E90" s="33"/>
+      <c r="F90" s="33">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="33">
         <v>1748</v>
       </c>
@@ -33262,8 +35628,15 @@
       <c r="C91" s="33">
         <v>2012</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91" s="33">
+        <v>1748</v>
+      </c>
+      <c r="E91" s="33"/>
+      <c r="F91" s="33">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="33">
         <v>3521</v>
       </c>
@@ -33271,8 +35644,15 @@
       <c r="C92" s="33">
         <v>1477</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92" s="33">
+        <v>3521</v>
+      </c>
+      <c r="E92" s="33"/>
+      <c r="F92" s="33">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="33">
         <v>3104</v>
       </c>
@@ -33280,8 +35660,15 @@
       <c r="C93" s="33">
         <v>3972</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D93" s="33">
+        <v>3104</v>
+      </c>
+      <c r="E93" s="33"/>
+      <c r="F93" s="33">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="33">
         <v>3533</v>
       </c>
@@ -33289,8 +35676,15 @@
       <c r="C94" s="33">
         <v>2038</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D94" s="33">
+        <v>3533</v>
+      </c>
+      <c r="E94" s="33"/>
+      <c r="F94" s="33">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="33">
         <v>3411</v>
       </c>
@@ -33298,8 +35692,15 @@
       <c r="C95" s="33">
         <v>995</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D95" s="33">
+        <v>3411</v>
+      </c>
+      <c r="E95" s="33"/>
+      <c r="F95" s="33">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="33">
         <v>1415</v>
       </c>
@@ -33307,8 +35708,15 @@
       <c r="C96" s="33">
         <v>2661</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D96" s="33">
+        <v>1415</v>
+      </c>
+      <c r="E96" s="33"/>
+      <c r="F96" s="33">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="33">
         <v>512</v>
       </c>
@@ -33316,8 +35724,15 @@
       <c r="C97" s="33">
         <v>1664</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D97" s="33">
+        <v>512</v>
+      </c>
+      <c r="E97" s="33"/>
+      <c r="F97" s="33">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="33">
         <v>1457</v>
       </c>
@@ -33325,8 +35740,15 @@
       <c r="C98" s="33">
         <v>3172</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D98" s="33">
+        <v>1457</v>
+      </c>
+      <c r="E98" s="33"/>
+      <c r="F98" s="33">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="33">
         <v>1025</v>
       </c>
@@ -33334,8 +35756,15 @@
       <c r="C99" s="33">
         <v>1408</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D99" s="33">
+        <v>1025</v>
+      </c>
+      <c r="E99" s="33"/>
+      <c r="F99" s="33">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="33">
         <v>1228</v>
       </c>
@@ -33343,8 +35772,15 @@
       <c r="C100" s="33">
         <v>825</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D100" s="33">
+        <v>1228</v>
+      </c>
+      <c r="E100" s="33"/>
+      <c r="F100" s="33">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="33">
         <v>3294</v>
       </c>
@@ -33352,8 +35788,15 @@
       <c r="C101" s="33">
         <v>833</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D101" s="33">
+        <v>3294</v>
+      </c>
+      <c r="E101" s="33"/>
+      <c r="F101" s="33">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="33">
         <v>3717</v>
       </c>
@@ -33361,8 +35804,15 @@
       <c r="C102" s="33">
         <v>3342</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D102" s="33">
+        <v>3717</v>
+      </c>
+      <c r="E102" s="33"/>
+      <c r="F102" s="33">
+        <v>3342</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="33">
         <v>605</v>
       </c>
@@ -33370,8 +35820,15 @@
       <c r="C103" s="33">
         <v>2065</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D103" s="33">
+        <v>605</v>
+      </c>
+      <c r="E103" s="33"/>
+      <c r="F103" s="33">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="33">
         <v>2121</v>
       </c>
@@ -33379,8 +35836,15 @@
       <c r="C104" s="33">
         <v>3466</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D104" s="33">
+        <v>2121</v>
+      </c>
+      <c r="E104" s="33"/>
+      <c r="F104" s="33">
+        <v>3466</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="33">
         <v>1504</v>
       </c>
@@ -33388,8 +35852,15 @@
       <c r="C105" s="33">
         <v>969</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D105" s="33">
+        <v>1504</v>
+      </c>
+      <c r="E105" s="33"/>
+      <c r="F105" s="33">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="33">
         <v>3440</v>
       </c>
@@ -33397,8 +35868,15 @@
       <c r="C106" s="33">
         <v>2290</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D106" s="33">
+        <v>3440</v>
+      </c>
+      <c r="E106" s="33"/>
+      <c r="F106" s="33">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="33">
         <v>2479</v>
       </c>
@@ -33406,8 +35884,15 @@
       <c r="C107" s="33">
         <v>3481</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D107" s="33">
+        <v>2479</v>
+      </c>
+      <c r="E107" s="33"/>
+      <c r="F107" s="33">
+        <v>3481</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="33">
         <v>1468</v>
       </c>
@@ -33415,8 +35900,15 @@
       <c r="C108" s="33">
         <v>2458</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D108" s="33">
+        <v>1468</v>
+      </c>
+      <c r="E108" s="33"/>
+      <c r="F108" s="33">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="33">
         <v>1845</v>
       </c>
@@ -33424,8 +35916,15 @@
       <c r="C109" s="33">
         <v>2378</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D109" s="33">
+        <v>1845</v>
+      </c>
+      <c r="E109" s="33"/>
+      <c r="F109" s="33">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="33">
         <v>713</v>
       </c>
@@ -33433,8 +35932,15 @@
       <c r="C110" s="33">
         <v>1190</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D110" s="33">
+        <v>713</v>
+      </c>
+      <c r="E110" s="33"/>
+      <c r="F110" s="33">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="33">
         <v>2390</v>
       </c>
@@ -33442,8 +35948,15 @@
       <c r="C111" s="33">
         <v>1161</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D111" s="33">
+        <v>2390</v>
+      </c>
+      <c r="E111" s="33"/>
+      <c r="F111" s="33">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="33">
         <v>1058</v>
       </c>
@@ -33451,8 +35964,15 @@
       <c r="C112" s="33">
         <v>2874</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D112" s="33">
+        <v>1058</v>
+      </c>
+      <c r="E112" s="33"/>
+      <c r="F112" s="33">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="33">
         <v>1731</v>
       </c>
@@ -33460,8 +35980,15 @@
       <c r="C113" s="33">
         <v>1865</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D113" s="33">
+        <v>1731</v>
+      </c>
+      <c r="E113" s="33"/>
+      <c r="F113" s="33">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="33">
         <v>1735</v>
       </c>
@@ -33469,8 +35996,15 @@
       <c r="C114" s="33">
         <v>2098</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D114" s="33">
+        <v>1735</v>
+      </c>
+      <c r="E114" s="33"/>
+      <c r="F114" s="33">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="33">
         <v>880</v>
       </c>
@@ -33478,8 +36012,15 @@
       <c r="C115" s="33">
         <v>2463</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D115" s="33">
+        <v>880</v>
+      </c>
+      <c r="E115" s="33"/>
+      <c r="F115" s="33">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="33">
         <v>1208</v>
       </c>
@@ -33487,8 +36028,15 @@
       <c r="C116" s="33">
         <v>2521</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D116" s="33">
+        <v>1208</v>
+      </c>
+      <c r="E116" s="33"/>
+      <c r="F116" s="33">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="33">
         <v>1897</v>
       </c>
@@ -33496,8 +36044,15 @@
       <c r="C117" s="33">
         <v>616</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D117" s="33">
+        <v>1897</v>
+      </c>
+      <c r="E117" s="33"/>
+      <c r="F117" s="33">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="33">
         <v>731</v>
       </c>
@@ -33505,8 +36060,15 @@
       <c r="C118" s="33">
         <v>1832</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D118" s="33">
+        <v>731</v>
+      </c>
+      <c r="E118" s="33"/>
+      <c r="F118" s="33">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="33">
         <v>930</v>
       </c>
@@ -33514,8 +36076,15 @@
       <c r="C119" s="33">
         <v>1200</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D119" s="33">
+        <v>930</v>
+      </c>
+      <c r="E119" s="33"/>
+      <c r="F119" s="33">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="33">
         <v>2408</v>
       </c>
@@ -33523,8 +36092,15 @@
       <c r="C120" s="33">
         <v>840</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D120" s="33">
+        <v>2408</v>
+      </c>
+      <c r="E120" s="33"/>
+      <c r="F120" s="33">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="33">
         <v>506</v>
       </c>
@@ -33532,8 +36108,15 @@
       <c r="C121" s="33">
         <v>2666</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D121" s="33">
+        <v>506</v>
+      </c>
+      <c r="E121" s="33"/>
+      <c r="F121" s="33">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="33">
         <v>1621</v>
       </c>
@@ -33541,43 +36124,50 @@
       <c r="C122" s="33">
         <v>2211</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D122" s="33">
+        <v>1621</v>
+      </c>
+      <c r="E122" s="33"/>
+      <c r="F122" s="33">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="33"/>
       <c r="B123" s="33"/>
       <c r="C123" s="33">
         <v>2891</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="33"/>
       <c r="B124" s="33"/>
       <c r="C124" s="33">
         <v>2920</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="33"/>
       <c r="B125" s="33"/>
       <c r="C125" s="33">
         <v>3686</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="33"/>
       <c r="B126" s="33"/>
       <c r="C126" s="33">
         <v>1400</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="33"/>
       <c r="B127" s="33"/>
       <c r="C127" s="33">
         <v>3556</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="33"/>
       <c r="B128" s="33"/>
       <c r="C128" s="33">
@@ -34038,6 +36628,18 @@
     <mergeCell ref="P1:R1"/>
     <mergeCell ref="I1:K1"/>
   </mergeCells>
+  <conditionalFormatting sqref="D4:D122">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="notBetween">
+      <formula>-1477</formula>
+      <formula>5752</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E61">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notBetween">
+      <formula>-319</formula>
+      <formula>4654</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
